--- a/sources/TOPCORE医院DDD8月28日.xlsx
+++ b/sources/TOPCORE医院DDD8月28日.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA74"/>
+  <dimension ref="A1:BB74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,13 @@
 焦虑医院试点医院</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="B1" t="inlineStr"/>
+      <c r="R1" t="inlineStr">
         <is>
           <t>与瞄准镜保持一致</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>注意合规表述</t>
         </is>
@@ -443,260 +444,265 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>试点标签</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>医院级别</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>DM</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>MICS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>准入标签</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>是否有进货金额限制</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>限制金额</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>院内渠道开放情况</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>3月tth预估实际</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>4月tth预估实际</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>5月tth预估实际</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>6月tth预估实际</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>7月tth预估实际</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>8月tth预估实际</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>梯队标签</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>月销量变化</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>头痛门诊/周</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>头痛客户数</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>眩晕门诊/周</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>眩晕门诊客户数</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>标签客户数</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>目标活跃客户数</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>活跃客户数</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>A客户</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>B客户</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>C客户</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>D客户</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>A客户贡献占比</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>B客户贡献占比</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>C客户贡献占比</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>D客户贡献占比</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>阶梯治疗</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>止痛优选</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>短期治痛</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>治痛管理</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>资深治痛管理</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>治痛管理大师</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>Q4目标月均梯队医院</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>9月TTH目标</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>目标A客户贡献预估</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>目标B客户贡献预估</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>目标C客户贡献预估</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>目标D客户贡献预估</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>目标阶梯治疗客户数</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>目标止痛优选客户数</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>目标短期治痛客户数</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>目标治痛管理客户数</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>目标资深治痛管理客户数</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>目标治痛管理大师客户数</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>洞察诊断</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>策略</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>针对各策略下客户增长及增长机会的具体行动计划</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>所需需求&amp;支持</t>
         </is>
@@ -708,240 +714,241 @@
           <t>江苏省人民医院</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>孟鈃</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>王方方/芦晓辉</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>his直连药店</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1124</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1208</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1204</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1184</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1476</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>1320</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
           <t>1500+</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>1、超代客户不稳定
 2、客户面拓展需扩大</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>1、超代客户通过系列会议和学科培养稳定产出
 2、分科室全面拓展，开发新客户</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>1. 针对存量超代客户，通过靶握周三会议与分层管理，保障业绩持续稳定产出。
 2. 针对增量市场，落实分科室全域拓展策略，开发新客户，实现客户规模与整体业务增量突破。</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>靶握周三会议、头痛病例集</t>
         </is>
@@ -953,143 +960,139 @@
           <t>苏州大学附属第一医院</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>何方禹</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>张桂香/陈利丰</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1086</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1048</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>908</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>1164</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1260</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>960</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1102,64 +1105,64 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>1500+</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>1080</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>636</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1167,30 +1170,35 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>1、TTH预估高度集中（赵&amp;王），4+4客户不足;
 2、B类客户诊断率低和推荐率低，无法推动正反馈持续使用经验；
 3、C类客户诊断率低，对于VM认知不足，需快速突破。</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>深做AC
 快拓BD</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>1、深做AC，A类客户：赵hr（治痛管理大师）持续提升；张qq（目标：治痛管理）提升推荐率和DOT，做好患者随访提升复购率，C类客户：王dp（治痛管理大师）做好患者随访提升复购率；于亚峰（目标：治痛管理）提升诊断率在VM和p-VM的患者上推荐使用，DOT3-6月的治疗周期，小C潘晨（目标：止痛优选）&amp;陶朵朵（目标：止痛优选）&amp;郭燕（目标：止痛优选）提升诊断率和推荐率。
 2、快拓B类客户：高潜力痛晕客户，实现止痛优选（薛sr、陈zg、王h、段xy、倪jq、高hq），持续推动提升诊断率和DOT;
 3、同步拓展神外：头痛潜力客户：陈zq（目标：止痛优选）</t>
         </is>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>1、平台与讲者：标杆医生区域讲者机会，学术会议搭建
 2、跨科联动：神内头痛中心-耳鼻喉眩晕-疼痛科多学科联动活动
@@ -1206,251 +1214,256 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>疼痛试点</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>孟鈃</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>罗世懿/李雪茹</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>正式准入</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>仅限神经内科</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>932</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>952</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>952</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>964</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1204</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>1244</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>2000+</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>1820</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>大A承担大部分产出，
 其余断层严重；B和C客户薄弱；D正在崛起</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>建立以大A为核心的mdt
 多学科头痛团队，院内资源合理化分配和利用；使得头痛患者在任何科室都不流失</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>1.头痛中心建立后的质控建设；
 2以清秀主任为核心的三方会交流、以孟老师为核心的mdtLB交流团结中青年；3.多学科互相流通；4.江北转诊机制</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>清秀主任全国平台打造</t>
         </is>
@@ -1464,165 +1477,165 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>焦虑抑郁试点</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>李路</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>王明月/白云松</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>正式准入</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>仅限门诊处方，病房未开通</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>931</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1024</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>906</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>933</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1144</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>989</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1630,86 +1643,91 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>1500+</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>1586</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>996</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>332</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AU6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>1、新A新增头痛门诊患者归拢率低；
 2、B转A，观念进展缓慢；
 3、C、D客户观念升级缓慢。</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>1、通过头痛小站、GD提升患者归拢率；
 2、积累正反馈病例，创造分享机会；
 3、通过讲师团强化观念，MDT会议加强融动。</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>1、新A强化患者归拢与管理，每月1场相关会议覆盖；
 2、B转A，客户每月一场病例主题会议，讨论或分享；
 3、覆盖陈G,赵XN,每季度1-2场升级治晕治痛观念。</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>每月1-2场省立牵头三方会议资源支持</t>
         </is>
@@ -1721,256 +1739,257 @@
           <t>苏州大学附属第二医院</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>何方禹</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>卢星翰</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>正式准入</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>18w/月</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>仅神经内科&amp;耳鼻喉科有权限处方</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>432</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>444</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>82%</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>院内单次处方限制及药占比影响
 C类客户面较少
 A类客户专家门诊虹吸效应不足且存在竞品在院内</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>院外药店引流减少药占比影响
 拓展C类客户面
 A类客户持续深挖，提高处方率</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>院外引流延长DOT减少限量影响
 协助完成偏头痛VM相关研究
@@ -1978,7 +1997,7 @@
 大型学术会议覆盖，提高科室头痛头晕知名度</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>医学部协助研究
 外部大型会议授课/主持提高头痛头晕知名度
@@ -1993,166 +2012,162 @@
           <t>青岛市市立医院</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>李明晖</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>472</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>492</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>456</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>460</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>484</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2160,65 +2175,70 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>1.专诊打造不足，增加头痛/眩晕专诊量，归拢患者
 2.提升足量足疗程观念，拓展患者画像
@@ -2226,20 +2246,20 @@
 4.组建MDT专家团队</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>1.融动神内和耳鼻喉客户增加专诊量2.明确患者画像，提供病例正反馈
 3.组建MDT专家团队，加强会议交流</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>1、增加专诊，提升患者归拢与管理
 2、C类客户明确患者画像，提高推荐率
 3、A/C类客户会议覆盖</t>
         </is>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>三方会主席/讲者/讨论</t>
         </is>
@@ -2253,159 +2273,159 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>焦虑抑郁试点</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>郑家成</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>徐燕</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>单患临采</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>392</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>460</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>365</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2418,65 +2438,70 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AU9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>1、头痛客户观念还有大幅升级空间，增加患者画像
 2、头晕客户观念薄弱，且参加会议意愿度较低，科室开展会议难度大
@@ -2484,14 +2509,14 @@
 4、精神科客户诊断差，观念薄弱</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>1、增加患者画像
 2、筛选客户
 3、提高客户诊断及观念</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>1、对于头痛客户分患者画像传递，逐一突破，增加患者画像使用 数
 2、对于眩晕客户，撬动其参会意愿度
@@ -2499,7 +2524,7 @@
 4、精神科客户多开展GD会，观念传递</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>1、线上会议（对于线下参会意愿度低的客户先洗刷观念）
 2、每周定期po会
@@ -2513,166 +2538,162 @@
           <t>南通大学附属医院</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>何方禹</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>周丽丽</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>316</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>444</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2680,70 +2701,75 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>528</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AU10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
           <t>南通大学附属医院为CORE医院，是东二区300+梯队的标杆核心院。tth由3月316稳定爬升至7月420，呈持续上行，月均已在300+梯队；9月TTH目标880、Q4月均目标800+，仍有翻倍增量空间。门诊结构：头痛门诊4个/周、头痛客户3人；眩晕门诊暂为0但眩晕客户5人（耳鼻喉眩晕方向）有基础。标签客户15人、活跃客户仅6人，沉睡池大。客户与观念呈「底重金字塔」：阶梯治疗1人、止痛优选3人、短期治痛1人、治痛管理仅1人（张鲁平），资深治痛管理/治痛管理大师均为0；A客户2人（蔡可夫、李爱红，贡献31.4%）、B客户2人（贡献8.6%）、C客户2人（张鲁平等，贡献60%）、D客户0。贡献高度集中——张鲁平(耳鼻喉眩晕C类)一人贡献近六成，9月目标300、7月已220，是绝对主力，但其观念已到治痛管理，需上推资深治痛管理；多数B类脑血管(柯开富、曹茂红、樊兴娟、倪耀辉、成亚琴、张元媛、张云峰、顾晓苏、赵映红)及D类其它科室(疼痛/其它)仍为「不管不治」，7月tth基本为0，是医院级最大未开发池。最大瓶颈：准入标签「未准入」，卡在处方最后一公里。</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>1) 头部巩固扩量：张鲁平(治痛管理→资深治痛管理)维持并借前庭性偏头痛专病/号源扩容做标杆；蔡可夫、李爱红(A类头痛)上推治痛管理；
 2) 中部观念上移：把止痛优选/短期治痛群体（柯开富、曹茂红、尤小东等）往治痛管理/短期治痛推，积累病例；
@@ -2752,12 +2778,12 @@
 5) 准入破冰：推动「未准入」转准入打通处方；补244标签、推动头痛/眩晕专诊与号源扩容做大患者池。</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>头部客户(张鲁平、蔡可夫、李爱红)每月≥2次高频拜访巩固并扩量，借前庭性偏头痛/头痛共病专诊扩容做大患者池并做转介网络；中部客户(柯开富、曹茂红、尤小东)依托专诊与科室会做观念上移、积累治痛管理病例；9名「不管不治」脑血管客户通过一场脑血管科室会+会后逐人破冰批量唤醒，并补全244标签(张元媛、张云峰、顾晓苏、缪秀华、李晓飞、郑冬冬等仍缺标签)；眩晕方向借区域眩晕会认前庭性偏头痛患者、优先瑞美吉泮用于血管风险者；D类(蒋锐、秦毅彬疼痛、李晓飞、郑冬冬)从其它科室培育，先以头痛/眩晕相关适应症切入；推动「未准入」转准入、开设/扩容头痛与眩晕专诊号源；对潜力但量未起的客户持续每月1-2次破冰拜访。</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>医学部循证（偏头痛-抑郁焦虑共病、前庭性偏头痛、血管风险、CGRP机制）资料与讲者支持；脑血管科室会+9人破冰带教支持；区域头痛/眩晕沙龙及COE会议名额；「未准入」转准入的医学/市场协同与院方准入协调；244标签系统录入与专诊/号源院方协调；张鲁平等头部客户的资深治痛管理上推与转介网络带教。</t>
         </is>
@@ -2769,151 +2795,147 @@
           <t>南通市第一人民医院</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>何方禹</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>周丽丽</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>396</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>332</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>392</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>0</t>
@@ -2926,59 +2948,59 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AU11" t="inlineStr">
         <is>
           <t>0</t>
@@ -2991,10 +3013,15 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>1.7月TTH 392，处于"300+"梯队，环比增长18.1%，连续2个月攀升，增长势能强劲，距500+梯队仅一步之遥；
 2.客户结构严重失衡：C类客户董政协1人贡献7月销量的94%（368/392），头部依赖风险极高；A类2人（朱向阳、杨家伟）合计仅贡献8，与分型定位严重不匹配；B类7人合计12，人均处方量极低；D类空白；
@@ -3003,7 +3030,7 @@
 5.观念层级分布：阶梯治疗4人、止痛优选0人、短期治痛0人、治痛管理0人、资深治痛管理1人、治痛管理大师0人，中高层观念客户稀缺，观念提升空间大。</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>策略一【头部维稳+标杆打造】：以董政协主任为核心，推动其从"资深治痛管理"向"治痛管理大师"进阶，打造前庭性偏头痛全程管理标杆，通过科室病例讨论、区域学术会议发挥辐射带动效应，确保核心贡献持续增长；
 策略二【A类激活+专诊转化】：重点激活朱向阳、杨家伟两位头痛专诊A类客户，加速观念从"不管不治/阶梯治疗"提升至"止痛优选/治痛管理"，推动专诊号源扩容与244标签建设，将专诊患者流量转化为处方量；
@@ -3011,7 +3038,7 @@
 策略四【耳鼻喉VM开发】：秦阳、吴昊两位耳鼻喉科头晕/眩晕客户，以前庭性偏头痛识别与鉴别诊断为切入点，推动眩晕专诊建设，拓展VM患者治疗覆盖。</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>1.9月协助董政协主任开展1次"前庭性偏头痛全程管理"科室病例讨论会，覆盖神内+耳鼻喉全体13位目标客户，目标带动≥3位B/C类客户观念提升；
 2.9月每周1次朱向阳头痛专诊前拜访，递送急性期+预防治疗指南，目标9月处方量从8提升至30，新增预防治疗患者2例；
@@ -3022,7 +3049,7 @@
 7.9月目标：全院TTH从392提升至500（+27.6%），活跃客户从5人增至9人，A类客户贡献占比从2%提升至15%。</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>1.学术资料：偏头痛急性期及预防性治疗最新指南/共识、前庭性偏头痛ICHD-3诊断标准及鉴别诊断流程图、脑血管病合并偏头痛共病管理文献、瑞美吉泮循证医学资料包（含2小时无痛率、长期安全性、MMD改善、心血管安全性数据）；
 2.会议支持：9月科室"前庭性偏头痛全程管理"病例讨论会（讲者课件、会议场地、参会激励），目标覆盖13位客户；区域学术会议/城市会讲者平台与参会名额；
@@ -3038,166 +3065,162 @@
           <t>苏州市立医院</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>何方禹</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>杜研</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>常备临采</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>344</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>392</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>43%</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>0</t>
@@ -3205,82 +3228,87 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AU12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>①活跃客户数不足：23位目标客户8月活跃仅10人(活跃率43%)，距目标20差10人；13人零处方(9位脑血管B类全零+沈明强断方+刘迎梅/沈蓉/吴冠会零)，空白巨大。
 ②止痛优选+观念客户少：止痛优选仅1人(邓邦鱼)、短期治痛2、治痛管理1，'观念客户'(止痛优选及以上)合计仅4/23；57%(13人)处'不管不治'底层，观念金字塔'底重'，是销量增长核心瓶颈。
 ③VM客户尤其耳鼻喉客户面少、深度不够：科室神内21+ENT1+其它1，耳鼻喉仅邓邦鱼1人；眩晕门诊0/周、VM(占眩晕15-20%)诊疗处方基本空白；邓邦鱼量36→20跌、刘迎梅断方、朱伟低量，VM'有方向无体系'。</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>1.头部A类稳量上移：付建忠(专诊8/月→资深/大师+预防渗透+GD会讲者/代言)、冯红选(专诊4→8扩容稳住+升代言)、王媚瑕(巩固起量+专诊扩容+升倡导)、沈明强(优先激活断方恢复+补244)。2.活跃客户扩容：9位沉睡脑血管B类(周华/王锋/邱晨红/邓晓雷/江玲玲/孙沁怡/丁园/黄开梅/朱浩)按'补244→STEP1打标签→差异化挂号杠杆→开专病门诊/增号源'批量破冰；高门诊零处方吴冠会(24/月)、沈蓉(8/月)优先PSR随访+打标签激活；王薇(16/月)补244撬动；目标Q4活跃10→20。3.观念金字塔上移+止痛优选扩容(补②)：Freezer→Tryer(13→≤3)、Tryer→Repeater止痛优选(1→≥3)、Advocator(2→≥6)、Ambassador(1→≥3)；以GD会+指南+病例统一抬升。4.VM/耳鼻喉专项突破(补③)：邓邦鱼设眩晕专诊+VM筛查稳量上移；朱伟VM筛查+跨科(神内→ENT)转诊；刘迎梅重启痛晕专诊模块+打标签激活；清单扩容新增1-2位ENT眩晕/VM KOL(见客户名单末行)，建VM筛查流程(ICHD-3)，严守Do/Don't(仅急性期、75mg按需、不超适应症、GCMA审批)。5.KOL金字塔与244扩容(补④)：244标签9→≥18/23(14位缺失优先补全)；代言(Ambassador)由2→3人(赵中/付建忠/冯红选)；倡导(Advocator)由2→≥6人(付建忠/冯红选/王媚瑕/邓朋/冯倩/邓邦鱼)；讲者TTT+GD会+区域会放大peer影响。</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>1.9月协助付建忠维持头痛专诊8/月满负荷，冯红选/王媚瑕专诊4→8扩容，赵中申请'头痛/情绪共病'专病门诊并增号源，门诊地图/互联网医院完成专诊标注。2.每次专诊/出诊前递送偏头痛预防治疗指南，月发作≥2次患者按指南评估预防需求，头部持续新增全程管理患者。3.9月以GD会开展1次科室'偏头痛全程管理'病例讨论会，付建忠/王媚瑕主讲，覆盖神内+耳鼻喉目标客户，会后1周未到场一对一补访。4.邓邦鱼推动设眩晕专诊+建VM筛查流程(ICHD-3)，朱伟/刘迎梅完善VM标签+跨科转诊，严守VM推广Do/Don't。5.9位沉睡脑血管B类(周华等)分批补全244标签+出诊简介标签(STEP1打标签)，按'科室会批量/一对一先行/区域会预热/开专病门诊/增模块号源'差异化杠杆破冰，推动不管不治→阶梯。6.吴冠会(24/月)优先PSR电话/微信随访既往患者重建信心并补244标签，王薇/沈蓉/沈明强补244标签撬动高门诊量；每次拜访带1典型病例强化规范治疗。7.清单扩容：摸排耳鼻喉眩晕/头痛亚专业新增1-2位目标医生(客户名单末行示意)，纳入244标签与VM专项管理。</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>1.偏头痛预防治疗最新指南/共识、前庭性偏头痛ICHD-3诊断标准、抑郁焦虑-偏头痛共病文献、瑞美吉泮循证包(2小时无痛率/安全性)。2.9月科室'偏头痛全程管理'GD会名额、GCMA审批幻灯片、讲者TTT赋能(付建忠/王媚瑕/冯红选)。3.门诊地图/互联网医院专诊标注资源、专病门诊/加号审批协调。4.244标签系统录入支持、出诊简介标签优化工具(STEP1)、VM筛查表/VM质控共识/眩晕专诊建设工具包(话术单页、VM宣教单页、随访工具、眩晕日记模板)。5.PSR对既往处方患者电话/微信随访模板+疗效反馈收集、零新处方医生入门培训包、首方信心建立工具、同伴经验分享。6.上级医院头痛中心会诊/转诊资源、区域头痛学科建设平台学术活动名额、ENT眩晕/VM专项学术资源。</t>
         </is>
@@ -3294,174 +3322,174 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>疼痛试点</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>卜先峰</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>杨胜运/许恺丽</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>正式准入</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>无限制</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>364</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>348</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK13" t="inlineStr">
         <is>
           <t>0</t>
@@ -3469,59 +3497,59 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="AR13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AT13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW13" t="inlineStr">
         <is>
           <t>0</t>
@@ -3529,20 +3557,25 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
           <t>升级AB客户观念，扩大cd客户面</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>AB客户强客情，学术观念升级，cd客户科室会议覆盖，学术观念共识</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
+      <c r="BA13" t="inlineStr">
         <is>
           <t>A客户通过系列会议打造专家圈层B客户强客情，以张龙主任牵头，打造专家圈 CD客户 拓展耳鼻喉科 疼痛科，开展科室会议，拓展客户面</t>
         </is>
       </c>
-      <c r="BA13" t="inlineStr">
+      <c r="BB13" t="inlineStr">
         <is>
           <t>1：安徽头痛小组系列会议2：脑血管主题系列会议</t>
         </is>
@@ -3554,161 +3587,157 @@
           <t>青岛市西海岸医院</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>陈彩虹</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>332</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>0</t>
@@ -3721,59 +3750,59 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AR14" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AU14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW14" t="inlineStr">
         <is>
           <t>0</t>
@@ -3781,20 +3810,25 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
           <t>1、医院为头痛中心大三甲医院，产品当前状态为未准入，院内渠道暂未开放 2、头痛、眩晕专诊已开设，每周头痛门诊1次、眩晕门诊1次，A/B/C/D类客户均有布局 3、神经内科、疼痛科、耳鼻喉科均覆盖为目标客户，部分医生已开展专诊，但还有大量医生处于“不管不治”低观念阶段 4、历史TTH月销量维持300+水平，A类核心客户张亮贡献主要销量，其余客户潜力未释放且处方不连续</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>1、优先推进产品院内准入做青医本部的工作，打通院内渠道2、深耕已有专诊的A/C类客户，巩固核心产出3、激活B/D类客户，推动低观念医生完成观念升级4、借力头痛/眩晕专诊门诊，落地规范化诊疗路径，挖掘增量患者5、分层管理客户，实现A客户稳住基本盘、B/C/D客户观念升阶</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>1、准入方面：对接本部同事跟进院内采购、药剂科，梳理准入流程，准备完整产品资料，每周四为拜访日，借助跨部门同事力量协助进院 2、核心A客户张亮维护：跟进头痛专诊运行，门诊宣传以及PSR患者管理，跨平台交流资深治痛管理理念 3、C类客户李宏：依托眩晕专诊，推动观念从短期治痛升级至治痛管理，挖掘VM患者增量；4、潜力客户激活：贾春燕、孟超等，传递阶梯治疗、止痛优选理念，尝试门诊患者教育；针对滕继军、杨丽英等未破冰客户，从病例和GD会议切入，破除不管不治现状 5、专诊赋能：头痛、眩晕专诊门诊，提供诊疗工具资料，协助识别标签患者；耳鼻喉杨博文、黄天桥拓展头晕头痛患者机会 6、月度跟踪TTH销量，对比9月目标，复盘各客户观念转化与处方变化</t>
         </is>
       </c>
-      <c r="BA14" t="inlineStr">
+      <c r="BB14" t="inlineStr">
         <is>
           <t>准入方面需要跨部门和领导协防</t>
         </is>
@@ -3806,116 +3840,112 @@
           <t>苏州市中医医院</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>何方禹</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>卢星翰</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>0</t>
@@ -3923,34 +3953,34 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
           <t>93%</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>0</t>
@@ -3958,14 +3988,14 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK15" t="inlineStr">
         <is>
           <t>0</t>
@@ -3973,54 +4003,54 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
           <t>1000+</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AN15" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AP15" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>0</t>
@@ -4028,28 +4058,33 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>诊断率较低，B\C采用阶梯疗法
 科内对于头痛头晕不是特别重视</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>定期覆盖科主任，提高其头痛眩晕观念得到科主任支持，助力A\C发展
 协助相关研究，提高科室知名度</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>通过协助入组研究延长DOT
 刘凯鸣、张甦琳影响PPPD和VM时间界限，提高共病诊断率</t>
         </is>
       </c>
-      <c r="BA15" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>江苏省眩晕学会任职
 医学部协助完成VM研究
@@ -4063,166 +4098,162 @@
           <t>南京市第一医院</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>郑家成</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>孙娟</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>直联药店</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>268</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
           <t>0</t>
@@ -4230,59 +4261,59 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AP16" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
+      <c r="AQ16" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="AR16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
+      <c r="AS16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
+      <c r="AT16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU16" t="inlineStr">
+      <c r="AV16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW16" t="inlineStr">
         <is>
           <t>0</t>
@@ -4290,20 +4321,25 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
           <t>A客户只有一个头痛专病门诊且观念在阶梯治疗阶段；B客户门诊患者类型比较杂无法聚拢患者；C专病门诊客户无处方经验导致不敢推荐，有经验的C客户无专病门诊导致患者类型不聚集，效率低</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>A客户迭代观念增加推荐，B客户收集正反馈提高认可度，C客户增加专病门诊</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
+      <c r="BA16" t="inlineStr">
         <is>
           <t>增加对A类的客情拜访并提供专业的指南等资料，并增加邀请参加会议的机会，内外结合一起迭代观念，后期也要增加专病门诊和相关人员，形成团队；B类客户更加关注门诊中偏头痛患者的回访，增加正反馈，及时复诊，增加医生的认可度和知名度；C类有经验的客户要增加专病门诊，聚拢患者，并和无经验的专病门诊客户联动，一带一输出正向观念，一起进步成长</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr">
+      <c r="BB16" t="inlineStr">
         <is>
           <t>老板随访、日常客情、学会任职、高质量三方会</t>
         </is>
@@ -4315,116 +4351,112 @@
           <t>昆山市第一人民医院</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>何方禹</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>黄义杰</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>0</t>
@@ -4432,44 +4464,44 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
           <t>67%</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>0</t>
@@ -4482,65 +4514,70 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
           <t>800+</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AP17" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="AR17" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>1.7月TTH 280，处于"低于300"梯队，距离300梯队仅一步之遥，增长势能强劲。
 2.A类仅1人（张炎）贡献占57%，头部依赖严重；B类9人，人均处方量低；C类4人完全空白；
@@ -4551,7 +4588,7 @@
 7.吴亚平（抑郁焦虑亚专业）门诊中偏头痛共病率高达30-50%，目前完全未识别和处方。</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>1：以张炎头痛专诊为核心，推动专诊号源扩容（4→6次/月）+预防性治疗渗透，打造科室学术标杆，发挥辐射带动作用；
 2：9位B类客户按状态分层运营——成长型（任洁明）上量、刚首方型（马召玺、杨华）稳量、断方型（钱小燕、张蕾）激活、零起步型（陆丽芸、缪桂华、王一鸣）首方、跨亚专业型（吴亚平）共病切入，目标9月B类活跃客户从2人提升至7人；
@@ -4559,7 +4596,7 @@
 4：以张炎主任为讲者，9月开展1次科室"偏头痛全程管理"病例讨论会，覆盖神内+耳鼻喉全体目标客户，推动整体观念层级上移，目标治痛管理及以上客户从1人增至3人。</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="BA17" t="inlineStr">
         <is>
           <t>1.9月协助张炎主任提交头痛专诊加号申请，目标专诊从4次/月增至8次/月；
 2.每次专诊前递送偏头痛预防性治疗指南/文献，目标9月新增预防治疗患者5例；
@@ -4577,7 +4614,7 @@
 10.每次拜访携带1个典型病例，持续强化规范治疗观念，推动客户观念层级逐阶上移。</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr">
+      <c r="BB17" t="inlineStr">
         <is>
           <t>1.偏头痛急性期最新指南/共识、前庭性偏头痛ICHD-3诊断标准、抑郁焦虑与偏头痛共病管理文献、瑞美吉泮循证医学资料包（含2小时无痛率、安全性）；
 2.会9月科室"偏头痛全程管理"病例讨论会，目标覆盖14位客户；
@@ -4596,161 +4633,157 @@
           <t>青岛市中医医院</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>冯雅琪</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>0</t>
@@ -4763,72 +4796,77 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>430</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="AR18" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AU18" t="inlineStr">
+      <c r="AV18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>AC客户产出为主；B客户潜力需要释放；
 目前仅有1位头痛客户，需要融动中青年客户转A；
 C客户处方客户多但稳定客户较少，需要培养大C客户</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>1.落地眩晕学会，借助学会搭建中医院MDT小圈子；
 2.目前眩晕出诊客户（马晓维、陈卫）需要进阶观念，Q4会议资源覆盖，病例分享；
@@ -4836,7 +4874,7 @@
 4.耳鼻喉科眩晕门诊与学会同步推动，同时加强病房管理，深挖耳鼻喉，培养稳定处方客户，及小C大C客户；（朱晓宁 葛洪洲 陈晓宇）</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>1.晓宁主任学会筹备中，9月沟通院外宴请；
 2.两位客户已上报DM，优先进行会议覆盖；
@@ -4844,7 +4882,7 @@
 4.对于耳鼻喉客户，继续系列会议的召开，进行病例积累，同步跟进朱主任进行门诊申请</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr">
+      <c r="BB18" t="inlineStr">
         <is>
           <t>眩晕学会需要RM DM、市场部进行协防；
 学会后期承接，会议资源的覆盖</t>
@@ -4859,169 +4897,169 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>疼痛试点</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>孟鈃</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>章智程</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>正式准入</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>除急诊，其他门诊、病房全开放</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>0</t>
@@ -5034,75 +5072,80 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
           <t>800+</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>960</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="AP19" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
+      <c r="AQ19" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr">
+      <c r="AR19" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AU19" t="inlineStr">
+      <c r="AV19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
           <t>1.门诊患者眩晕客户目前观念阶梯治疗，复诊率低2.病房使用瑞美吉泮的患者出院带药低，复诊率低 3.疼痛科因治疗费无法降瑞美吉泮加入到方案</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>1.和随访护士一起沟通，或者帮助随访，看看是否真实有随访，邀约复诊 2.对没有随访护士的病区，融动主任建立随访机制，或帮助随访 3.尝试引进小包装，与疼痛科融合治疗方案</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>1.会议赞助 2.荣院和肖需要三方会议</t>
         </is>
@@ -5114,116 +5157,112 @@
           <t>江苏省苏北人民医院</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>郑家成</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>高佳怡</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>0</t>
@@ -5231,44 +5270,44 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
           <t>81%</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AH20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>0</t>
@@ -5281,59 +5320,59 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="AP20" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="AP20" t="inlineStr">
+      <c r="AQ20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr">
+      <c r="AR20" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AS20" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AT20" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="AU20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU20" t="inlineStr">
+      <c r="AV20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW20" t="inlineStr">
         <is>
           <t>0</t>
@@ -5341,20 +5380,25 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
           <t>眩晕客户产出占比不够</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>耳鼻喉，神内眩晕重点跟进</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
+      <c r="BA20" t="inlineStr">
         <is>
           <t>市人医眩晕中心，苏北眩晕门诊</t>
         </is>
       </c>
-      <c r="BA20" t="inlineStr">
+      <c r="BB20" t="inlineStr">
         <is>
           <t>眩晕三方会，lb</t>
         </is>
@@ -5366,156 +5410,152 @@
           <t>青岛大学附属医院</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>冯雅琪</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>164</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI21" t="inlineStr">
         <is>
           <t>0</t>
@@ -5533,54 +5573,54 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AP21" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr">
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="AQ21" t="inlineStr">
+      <c r="AR21" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AT21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="AU21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>0</t>
@@ -5592,12 +5632,17 @@
         </is>
       </c>
       <c r="AX21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>目前本部医院无头痛方向客户；客户处方面及深度急需拓展深挖；
 增长较为缓慢</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>对于已破冰处方客户，会议覆盖加深治痛治晕观念；
 筛选中青年客户，融动头痛眩晕方向发展；（王乃东/孙绍洋？）
@@ -5605,7 +5650,7 @@
 分客户拓展，共岗深挖客户潜力；</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
+      <c r="BA21" t="inlineStr">
         <is>
           <t>1.破冰客户已梳理名单，报给DM，三方会议覆盖；
 2.锁定王乃东/孙绍洋，做初步融动
@@ -5613,7 +5658,7 @@
 4.共岗客户名单已梳理，沟通中</t>
         </is>
       </c>
-      <c r="BA21" t="inlineStr">
+      <c r="BB21" t="inlineStr">
         <is>
           <t>DM及市场部、区域部共同协防孙妍萍主任及药剂科
 推动青医临采</t>
@@ -5626,116 +5671,112 @@
           <t>山东大学齐鲁医院</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
         <is>
           <t>TOP</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>李路</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>313</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>0</t>
@@ -5743,34 +5784,34 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>0</t>
@@ -5793,49 +5834,49 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AN22" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
+      <c r="AP22" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="AP22" t="inlineStr">
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr">
+      <c r="AR22" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
+      <c r="AS22" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AT22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AU22" t="inlineStr">
         <is>
           <t>0</t>
@@ -5852,27 +5893,32 @@
         </is>
       </c>
       <c r="AX22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
         <is>
           <t>1、A客户对于六类优势人群未常规首选；
 2、B对于单患者未达足剂量；
 3、CD观念夯实不稳固。</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>1、学术会议影响观念，推动新的优势人群的认知；
 2、强化患者后续风险，做好患者管理；
 3、由AB影响改变CD的观念。</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
+      <c r="BA22" t="inlineStr">
         <is>
           <t>1、倡导六大优势人群常规首选，每月一场相关主题的会议；
 2、相应群体确保足剂量足疗程，每月一场患教会传递，做好头痛日记的管理；
 3、分享AB应用经验，每月围绕目标客户2场科室会。</t>
         </is>
       </c>
-      <c r="BA22" t="inlineStr">
+      <c r="BB22" t="inlineStr">
         <is>
           <t>每月1-2场三方会议覆盖含主席、讲者及讨论的名额</t>
         </is>
@@ -5884,151 +5930,147 @@
           <t>潍坊市人民医院</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AH23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI23" t="inlineStr">
         <is>
           <t>0</t>
@@ -6046,54 +6088,54 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr">
+      <c r="AQ23" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AR23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AT23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="AU23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>0</t>
@@ -6106,20 +6148,25 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
           <t>1、无核心专业的头痛医生，缺乏科室级学术标杆2、现有客户深度不够、缺少学术绑定，足量足疗程管理认知不深3、C类客户基数少、潜力未发觉</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>1、筛选科室意向高、学习意愿强的中青年医生，孵化为A类客户2、从单纯拜访 升级为学术绑定+诊疗观念统一。通过病例复盘、足量足疗程观念输出、打造核心B客户群 3、针对神内与耳鼻喉的眩晕中心进行广覆盖、扩充客户基数</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
+      <c r="BA23" t="inlineStr">
         <is>
           <t>1、梳理未定专业以及对头痛感兴趣的青年医师，锁定2-3位进行重点管理客户。优先邀请参加相关会议，、2、协助科室梳理诊疗流程、患者管理体系，打造科室特色亚专业3、4季度完成A客户打造、带动科室整体观念4、针对核心B客户，每周1次深度拜访。每次输出1个临床痛点、融动一个患者画像5、主动协助客户梳理门户患者病例，9月完成1-2例的典型病例，做好足量足疗程管路6、代言客户定制客户计划、提升客户认可度以及依赖度7、广覆盖C客户，开展常态化GD，低成本观念触达，筛选2-3位核心客户进行深度缔结，培养足量足疗程习惯</t>
         </is>
       </c>
-      <c r="BA23" t="inlineStr">
+      <c r="BB23" t="inlineStr">
         <is>
           <t>线上会一场，做耳鼻喉眩晕与神内眩晕的MDT，打通医院诊疗</t>
         </is>
@@ -6131,156 +6178,152 @@
           <t>淄博市中心医院</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>鲁景霄</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI24" t="inlineStr">
         <is>
           <t>0</t>
@@ -6298,54 +6341,54 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="AP24" t="inlineStr">
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AT24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="AU24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>0</t>
@@ -6358,20 +6401,25 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
           <t>偏头痛诊断率较低，阶梯治疗观念，瑞美推荐等级较低</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>A客户头痛专病门诊深挖，B类客户提升偏头痛诊断率，提升瑞美推荐等级，C类客户提升VM诊断率，明确目标患者画像</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
+      <c r="BA24" t="inlineStr">
         <is>
           <t>A客户头痛门诊CDSS提升病例规范化，深挖偏头痛患者潜力，覆盖PO及三方会议，B客户覆盖会议，提升偏头痛诊断率及瑞美推荐等级，C重点客户优先覆盖三方会议，外部观念影响，PSR协助随访患者，提升正反馈</t>
         </is>
       </c>
-      <c r="BA24" t="inlineStr">
+      <c r="BB24" t="inlineStr">
         <is>
           <t>PO会议讲者。三方会议讲者或讨论</t>
         </is>
@@ -6383,81 +6431,77 @@
           <t>山东第二医科大学附属医院</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>青岛</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T25" t="inlineStr">
         <is>
           <t>0</t>
@@ -6465,74 +6509,74 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>0</t>
@@ -6545,54 +6589,54 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="AP25" t="inlineStr">
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AS25" t="inlineStr">
+      <c r="AT25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>0</t>
@@ -6605,16 +6649,21 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
           <t>1、头痛专诊患者归拢率低2、现有核心客户足量足疗程规范化观念薄弱3、眩晕科客户覆盖率低、潜力挖掘不足</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>1、协助科室沉淀头痛专病接诊体系，引导患者归拢，打造固定专病流量端口2、以病例随访+指南落地双抓手，纠正短期用药习惯，统一足量、足疗程、长周期管理理念
 不单纯做产品拜访3、眩晕科客户全面盘点、覆盖、打造科室第二增长曲线</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
+      <c r="BA25" t="inlineStr">
         <is>
           <t>1、对接科室主任及核心骨干，沟通头痛亚专业规范化建设思路、开展科室小型宣教，明确典型偏头痛、复发性头痛患者的专病接诊路径，引导门诊分诊集中。2、对现有A/B核心客户执行一对一学术深耕拜访，每次拜访聚焦一个主题、核心客户全部建立足量足疗程、长周期管理的规范化诊疗习惯，患者复发率下降、持续用药率提升、3、对空白客户完成首轮学术触达，普及VM与各类眩晕的鉴别诊断、规范化用药基础认知，完成基础扫盲。4、筛选2–3名优质潜力客户，重点跟进、重点学术倾斜，通过病例分享、指南推送、门诊沟通，逐步培养眩晕处方习惯。</t>
         </is>
@@ -6626,156 +6675,152 @@
           <t>安徽省立医院</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>卜先峰</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>洪剑</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>164</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB26" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AH26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI26" t="inlineStr">
         <is>
           <t>0</t>
@@ -6793,49 +6838,49 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AP26" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AP26" t="inlineStr">
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AT26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr">
+      <c r="AU26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>0</t>
@@ -6848,20 +6893,25 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
           <t>诊断观念落后不明确，推荐率低，院外药房到店率低</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>提高偏头痛的诊断率和推荐率，药房培训和协助，管理随访</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
+      <c r="BA26" t="inlineStr">
         <is>
           <t>围绕安徽省头痛小组建设发展，积极拓展科室头痛人员观念，眩晕中心建设安徽省的标杆，打造全省到全国的影响力</t>
         </is>
       </c>
-      <c r="BA26" t="inlineStr">
+      <c r="BB26" t="inlineStr">
         <is>
           <t>头痛专向会议覆盖，以安徽省眩晕中心建设开展VM的专向治疗标准和观念</t>
         </is>
@@ -6873,161 +6923,157 @@
           <t>徐州医科大学附属医院</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>孟鈃</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>章智程</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>处方外配</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
           <t>0</t>
@@ -7040,75 +7086,80 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
           <t>500+</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AN27" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AP27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AP27" t="inlineStr">
+      <c r="AQ27" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="AQ27" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AS27" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
+      <c r="AU27" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AU27" t="inlineStr">
+      <c r="AV27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV27" t="inlineStr">
+      <c r="AW27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AX27" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
           <t>1.头痛中心主任不重视头痛专病门诊没有稳定开展2.大量患者流到老专家观念比较差的客户手里 3.眩晕中心诊断不规范</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>1.融动头痛中心主任积极发展中心。2.其他可以申请头痛专病门诊的科室筛选愿意积极发展的中青年专家开展头痛专病门诊 3.眩晕中心诊断策略需要改变，从患者角度和治疗角度推荐使用瑞美吉泮</t>
         </is>
       </c>
-      <c r="BA27" t="inlineStr">
+      <c r="BB27" t="inlineStr">
         <is>
           <t>LB、三方会</t>
         </is>
@@ -7120,166 +7171,162 @@
           <t>常州市第一人民医院</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>郑家成</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>缪苏琴</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK28" t="inlineStr">
         <is>
           <t>0</t>
@@ -7287,83 +7334,88 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AP28" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AP28" t="inlineStr">
+      <c r="AQ28" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="AQ28" t="inlineStr">
+      <c r="AR28" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AS28" t="inlineStr">
+      <c r="AT28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AU28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
         <is>
           <t>1、头痛门诊医生经验不足，对头痛的诊断和识别能力较差
 2、客户面太少需要拓展</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>1、A类客户要加大宣传，增加会议覆盖，并做好跟进；
 2、B类客户迭代观念，从阶梯治疗到治痛管理</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
+      <c r="BA28" t="inlineStr">
         <is>
           <t>1、区域中青年PO会计划执行，做好会后跟进
 2、客户数拓展后加强拜访频率</t>
         </is>
       </c>
-      <c r="BA28" t="inlineStr">
+      <c r="BB28" t="inlineStr">
         <is>
           <t>会议覆盖、学苑培训班</t>
         </is>
@@ -7375,156 +7427,152 @@
           <t>东南大学附属中大医院</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>郑家成</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>孙娟</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>直联药店</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AB29" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI29" t="inlineStr">
         <is>
           <t>0</t>
@@ -7542,54 +7590,54 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AN29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="AP29" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AP29" t="inlineStr">
+      <c r="AQ29" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR29" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AT29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr">
+      <c r="AU29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>0</t>
@@ -7602,20 +7650,25 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
           <t>每周2个头痛门诊，但是都有其他专业一起；耳鼻喉科客户观念较差</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>A类客户要加大宣传，增加专诊次数，并做好回访；C类客户迭代观念，从阶梯治疗到治痛管理</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
+      <c r="BA29" t="inlineStr">
         <is>
           <t>A类客户在门诊屏幕、分诊台做好分流，督促做好患者回访及时复诊，归拢患者收集正反馈；C类客户邀请参加内外部会议更新观念，改变处方习惯</t>
         </is>
       </c>
-      <c r="BA29" t="inlineStr">
+      <c r="BB29" t="inlineStr">
         <is>
           <t>三方会、GD/LB/PO、头痛头晕量表收集</t>
         </is>
@@ -7629,69 +7682,69 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>焦虑抑郁试点</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>李路</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>公茂伟</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>未准入</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>0</t>
@@ -7709,24 +7762,24 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>0</t>
@@ -7739,44 +7792,44 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AG30" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI30" t="inlineStr">
         <is>
           <t>0</t>
@@ -7794,24 +7847,24 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AN30" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AP30" t="inlineStr">
         <is>
           <t>0</t>
@@ -7819,29 +7872,29 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="AR30" t="inlineStr">
+      <c r="AS30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AS30" t="inlineStr">
+      <c r="AT30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr">
+      <c r="AU30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>0</t>
@@ -7853,27 +7906,32 @@
         </is>
       </c>
       <c r="AX30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>1成立头痛门诊
 2增加MDT联合诊疗观念
 3增加治痛观念进阶医生</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>1融动院长计划引进头痛专家计划
 2成立融合门诊MDT诊断
 3优秀病例分享圈</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
+      <c r="BA30" t="inlineStr">
         <is>
           <t>1以实现人才引进
 2加速融合MDT圈子认识
 3开始积累病例</t>
         </is>
       </c>
-      <c r="BA30" t="inlineStr">
+      <c r="BB30" t="inlineStr">
         <is>
           <t>每月2个名额参与三方会</t>
         </is>
@@ -7887,79 +7945,79 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>焦虑抑郁试点</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>张鑫</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>李明晖</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>批量临采</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T31" t="inlineStr">
         <is>
           <t>0</t>
@@ -7972,19 +8030,19 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>0</t>
@@ -7997,44 +8055,44 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI31" t="inlineStr">
         <is>
           <t>0</t>
@@ -8052,19 +8110,19 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AN31" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>0</t>
@@ -8077,29 +8135,29 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="AR31" t="inlineStr">
+      <c r="AS31" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AS31" t="inlineStr">
+      <c r="AT31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr">
+      <c r="AU31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>0</t>
@@ -8111,24 +8169,29 @@
         </is>
       </c>
       <c r="AX31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
         <is>
           <t>1.D类客户既往无偏头痛诊断经验，偏头痛观念不足
 2.无A类客户，头痛专诊数不足</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>1、通过GD会议，邀请参加三方会听课学习提升偏头痛诊断率；
 2、积累正反馈病例，创造分享机会；与综合医院A类客户建立交流平台
 3、增加专病门诊</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
+      <c r="BA31" t="inlineStr">
         <is>
           <t>1.利用GD会，三方会提升客户的偏头痛诊断观念2.组建MDT团队，提供病例正反馈提升用药信心</t>
         </is>
       </c>
-      <c r="BA31" t="inlineStr">
+      <c r="BB31" t="inlineStr">
         <is>
           <t>三方会议讲者/讨论</t>
         </is>
@@ -8140,116 +8203,112 @@
           <t>胜利油田中心医院</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>李路</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>于彦文</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>常备临采</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>门诊使用</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>416</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>268</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>低于300</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Z32" t="inlineStr">
         <is>
           <t>0</t>
@@ -8262,34 +8321,34 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>0</t>
@@ -8312,44 +8371,44 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
           <t>300+</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AN32" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="AP32" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="AP32" t="inlineStr">
+      <c r="AQ32" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="AR32" t="inlineStr">
+      <c r="AS32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AT32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AU32" t="inlineStr">
         <is>
           <t>0</t>
@@ -8367,67 +8426,156 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
           <t>1，该岗位空岗时间长，总体客户数以及活跃客户数不足，2客户治痛理念不够，3C客户待开发</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>1，增加覆盖，更多客户破冰 2，客户观念进阶3，开发c客户</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
+      <c r="BA32" t="inlineStr">
         <is>
           <t>1，每天跟进重点KOL拜访，9月GD会召开，建立客户基本理念增加破冰客户。2，使用经验的客户收集正反馈，促使客户快速进阶。3，C客户借助齐鲁眩晕行做一场巡讲</t>
         </is>
       </c>
-      <c r="BA32" t="inlineStr">
+      <c r="BB32" t="inlineStr">
         <is>
           <t>1，新员工能力提升-培训部和市场部支持。2，市场重点选择5个客户给学术会议观念改变。9月AC客户会议名额。</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
+    <row r="33">
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sources/TOPCORE医院DDD8月28日.xlsx
+++ b/sources/TOPCORE医院DDD8月28日.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB74"/>
+  <dimension ref="A1:BD74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +707,16 @@
           <t>所需需求&amp;支持</t>
         </is>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>半月内重点三件事</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>半个月内GD/LB规划</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -757,7 +767,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -797,7 +807,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -807,7 +817,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -842,7 +852,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -862,12 +872,12 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1005,7 +1015,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1040,12 +1050,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1055,17 +1065,17 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1090,7 +1100,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1188,7 +1198,8 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>深做AC
-快拓BD</t>
+快拓BD
+渠道优化</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1201,8 +1212,15 @@
       <c r="BB4" t="inlineStr">
         <is>
           <t>1、平台与讲者：标杆医生区域讲者机会，学术会议搭建
-2、跨科联动：神内头痛中心-耳鼻喉眩晕-疼痛科多学科联动活动
+2、跨科联动：神内头痛中心-耳鼻喉眩晕-神经外科多学科联动活动
 3、准入与渠道：推动进院/临时采购或外配流转，打通处方最后一公里；</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>1、
+2、
+3、拓面TDD这个客户</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1290,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1312,7 +1330,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1322,7 +1340,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1357,7 +1375,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1533,7 +1551,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1618,12 +1636,12 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1802,7 +1820,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>520</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1977,32 +1995,34 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>院内单次处方限制及药占比影响
-C类客户面较少
-A类客户专家门诊虹吸效应不足且存在竞品在院内</t>
+          <t>1.活跃客户数少，止痛优选+观念客户少
+2.耳鼻喉客户面和客户深度不足
+3.院内限制及药占比影响DOT不足</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>院外药店引流减少药占比影响
-拓展C类客户面
-A类客户持续深挖，提高处方率</t>
+          <t>1.神内全覆盖，A类客户持续深挖，提高处方率
+2.拓展C类客户面 
+3.院外药店引流减少药占比影响
+4.制作偏头痛相关物料提高效率</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>院外引流延长DOT减少限量影响
-协助完成偏头痛VM相关研究
-PSR每月定期复盘，共识目标，解决需求
-大型学术会议覆盖，提高科室头痛头晕知名度</t>
+          <t>1.PSR每月定期复盘，共识目标，解决需求提高复诊率40到80，成功率70-80
+2.利用3场GD做到绝大部分B类客户全覆盖，告神经内科刚开展前庭功能检查，耳鼻喉科竞争关系抓住头晕为主诉患者联合用药防止患者流失。
+3.院外引流延长DOT减少限量影响
+4.大型院间学术会议覆盖，提高科室头痛头晕知名度，得到刘院长、毛主任支持。毛主任标准偏头痛患者引流到李、徐提高头痛门诊归拢率
+5、制作偏头痛用药副作用一览表、患教手册、日记等纸质材料提高对比竞品竞争力，注重全程管理治痛治晕</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>医学部协助研究
-外部大型会议授课/主持提高头痛头晕知名度
-PO、三方覆盖
-省级学会活动参与任职</t>
+          <t>1.医学部协助共访
+2.外部大型会议授课/主持，NHC项目讲师，提高头痛三人组头痛头晕知名度
+3.PO、三方覆盖
+4.未有任职A\C客户重点省级学会活动参与任职</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2085,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>504</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2328,7 +2348,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>385</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2591,7 +2611,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>456</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2711,7 +2731,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2741,12 +2761,12 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2772,20 +2792,19 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>1) 头部巩固扩量：张鲁平(治痛管理→资深治痛管理)维持并借前庭性偏头痛专病/号源扩容做标杆；蔡可夫、李爱红(A类头痛)上推治痛管理；
-2) 中部观念上移：把止痛优选/短期治痛群体（柯开富、曹茂红、尤小东等）往治痛管理/短期治痛推，积累病例；
-3) 底部批量破冰：9名B类脑血管「不管不治」客户（樊兴娟、倪耀辉、成亚琴、张元媛、张云峰、顾晓苏、赵映红等）通过一场脑血管科室会+逐人破冰批量唤醒进阶梯治疗；
-4) 渠道借力：依托头痛专诊(蔡可夫4/周、李爱红8/周、陈鑫4/周)做治痛管理路径示范；眩晕方向(张鲁平、尤小东、胡松群、殷勇、刘浩)攻前庭性偏头痛血管风险患者；
-5) 准入破冰：推动「未准入」转准入打通处方；补244标签、推动头痛/眩晕专诊与号源扩容做大患者池。</t>
+2) 观念上移：把止痛优选/短期治痛群体（柯开富、曹茂红、尤小东等）往治痛管理/短期治痛推，积累病例；
+3) B:9名B类脑血管「不管不治」客户（樊兴娟、倪耀辉、成亚琴、张元媛、张云峰、顾晓苏、赵映红等）gd覆盖
+4) 依托头痛专诊(蔡可夫4/周、李爱红8/周、陈鑫4/周)做治痛管理路径示范；眩晕方向(张鲁平、尤小东、胡松群、殷勇、刘浩)攻前庭性偏头痛血管风险患者；</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>头部客户(张鲁平、蔡可夫、李爱红)每月≥2次高频拜访巩固并扩量，借前庭性偏头痛/头痛共病专诊扩容做大患者池并做转介网络；中部客户(柯开富、曹茂红、尤小东)依托专诊与科室会做观念上移、积累治痛管理病例；9名「不管不治」脑血管客户通过一场脑血管科室会+会后逐人破冰批量唤醒，并补全244标签(张元媛、张云峰、顾晓苏、缪秀华、李晓飞、郑冬冬等仍缺标签)；眩晕方向借区域眩晕会认前庭性偏头痛患者、优先瑞美吉泮用于血管风险者；D类(蒋锐、秦毅彬疼痛、李晓飞、郑冬冬)从其它科室培育，先以头痛/眩晕相关适应症切入；推动「未准入」转准入、开设/扩容头痛与眩晕专诊号源；对潜力但量未起的客户持续每月1-2次破冰拜访。</t>
+          <t>头部客户(张鲁平、蔡可夫、李爱红)每月≥2次高频拜访，提高前庭性偏头痛诊断，全流程管理；中部客户(柯开富、曹茂红、尤小东)标签添加、积累治痛管理病例；9名「不管不治」脑血管客户通过GD，PO+会后覆盖并补全244标签(张元媛、张云峰、顾晓苏、缪秀华、李晓飞、郑冬冬等仍缺标签)；眩晕方向借区域眩晕会认前庭性偏头痛患者、优先瑞美吉泮用于血管风险者；D类(蒋锐、秦毅彬疼痛、李晓飞、郑冬冬)从其它科室培育；对潜力但量未起的客户持续每月1-2次破冰拜访。</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>医学部循证（偏头痛-抑郁焦虑共病、前庭性偏头痛、血管风险、CGRP机制）资料与讲者支持；脑血管科室会+9人破冰带教支持；区域头痛/眩晕沙龙及COE会议名额；「未准入」转准入的医学/市场协同与院方准入协调；244标签系统录入与专诊/号源院方协调；张鲁平等头部客户的资深治痛管理上推与转介网络带教。</t>
+          <t>AC客户：圈层搭建，省级以上学会任职，全国区域区域会议讲者。B/D中青年客户，亚专业相同的领域参会/讲课平台，提升对偏头痛领域的兴趣。RM/DM/LMM协防</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2867,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>352</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2883,112 +2902,112 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>1000+</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>700+</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
         <is>
           <t>2%</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>1000+</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -3033,15 +3052,15 @@
       <c r="AZ11" t="inlineStr">
         <is>
           <t>策略一【头部维稳+标杆打造】：以董政协主任为核心，推动其从"资深治痛管理"向"治痛管理大师"进阶，打造前庭性偏头痛全程管理标杆，通过科室病例讨论、区域学术会议发挥辐射带动效应，确保核心贡献持续增长；
-策略二【A类激活+专诊转化】：重点激活朱向阳、杨家伟两位头痛专诊A类客户，加速观念从"不管不治/阶梯治疗"提升至"止痛优选/治痛管理"，推动专诊号源扩容与244标签建设，将专诊患者流量转化为处方量；
-策略三【B类分层运营】：7位B类客户按状态分层——成长型（李燕、陈蓝）上量、断方型（朱连海）激活、零起步型（曹志勇、陆珍辉、郭啸鸣、邵良、汪晗）破冰，以"脑血管病合并偏头痛共病管理"为统一切入点，提升整体活跃率与人均处方量；
+策略二【A类+专诊转化】：重点朱向阳、杨家伟两位头痛专诊A类客户，加速观念从"不管不治/阶梯治疗"提升至"止痛优选/治痛管理"；
+策略三【B类分层运营】：7位B类客户按状态分层以"脑血管病合并偏头痛共病管理"为统一切入点
 策略四【耳鼻喉VM开发】：秦阳、吴昊两位耳鼻喉科头晕/眩晕客户，以前庭性偏头痛识别与鉴别诊断为切入点，推动眩晕专诊建设，拓展VM患者治疗覆盖。</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1.9月协助董政协主任开展1次"前庭性偏头痛全程管理"科室病例讨论会，覆盖神内+耳鼻喉全体13位目标客户，目标带动≥3位B/C类客户观念提升；
-2.9月每周1次朱向阳头痛专诊前拜访，递送急性期+预防治疗指南，目标9月处方量从8提升至30，新增预防治疗患者2例；
+          <t>1.9月协助董政协主任开展1次"前庭性偏头痛全程管理"病例讨论会，覆盖神内+耳鼻喉全体6位目标客户，目标带动≥3位B/C类客户观念提升；
+2.9月每周1次朱向阳头痛专诊前拜访，传递指南，目标9月处方量从8提升至30，新增预防治疗患者2例；
 3.9月优先安排杨家伟深度回访，分析断方原因并制定激活方案，目标9月重新实现首方并稳定至≥4例患者；
 4.9月对7位B类客户实施分层拜访：成长型每两周1次聚焦上量、断方型优先1次深度回访+每两周1次激活、零起步型每两周1次破冰，目标9月B类活跃客户从2人增至5人；
 5.9月协同秦阳、吴昊推动耳鼻喉科眩晕专诊建设，以前庭性偏头痛鉴别诊断为学术抓手，目标9月秦阳稳定处方≥4例、吴昊实现首方≥2例；
@@ -3051,11 +3070,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1.学术资料：偏头痛急性期及预防性治疗最新指南/共识、前庭性偏头痛ICHD-3诊断标准及鉴别诊断流程图、脑血管病合并偏头痛共病管理文献、瑞美吉泮循证医学资料包（含2小时无痛率、长期安全性、MMD改善、心血管安全性数据）；
-2.会议支持：9月科室"前庭性偏头痛全程管理"病例讨论会（讲者课件、会议场地、参会激励），目标覆盖13位客户；区域学术会议/城市会讲者平台与参会名额；
-3.物料支持：头痛/眩晕专诊患者随访登记表、MMD记录卡、患者教育手册、门诊头痛快速筛查表（含心血管风险评估模块）、瑞美吉泮临床数据速查卡；
-4.院方协调：专诊号源扩容审批支持、244标签及出诊简介标签系统录入支持；
-5.人力资源：MICS/DM/RPM协同拜访资源（重点支持破冰客户与断方激活）、上级医院头痛/眩晕中心专家会诊/转诊对接、新人破冰拜访带教支持。</t>
+          <t>偏头痛急性期及预防性治疗最新指南/共识、前庭性偏头痛ICC客户：圈层搭建，省级以上学会任职，全国区域区域会议讲者。B/D中青年客户，亚专业相同的领域参会/讲课平台，提升对偏头痛领</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3133,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>408</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3128,7 +3143,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3143,7 +3158,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -3158,52 +3173,52 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -3300,17 +3315,28 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1.头部A类稳量上移：付建忠(专诊8/月→资深/大师+预防渗透+GD会讲者/代言)、冯红选(专诊4→8扩容稳住+升代言)、王媚瑕(巩固起量+专诊扩容+升倡导)、沈明强(优先激活断方恢复+补244)。2.活跃客户扩容：9位沉睡脑血管B类(周华/王锋/邱晨红/邓晓雷/江玲玲/孙沁怡/丁园/黄开梅/朱浩)按'补244→STEP1打标签→差异化挂号杠杆→开专病门诊/增号源'批量破冰；高门诊零处方吴冠会(24/月)、沈蓉(8/月)优先PSR随访+打标签激活；王薇(16/月)补244撬动；目标Q4活跃10→20。3.观念金字塔上移+止痛优选扩容(补②)：Freezer→Tryer(13→≤3)、Tryer→Repeater止痛优选(1→≥3)、Advocator(2→≥6)、Ambassador(1→≥3)；以GD会+指南+病例统一抬升。4.VM/耳鼻喉专项突破(补③)：邓邦鱼设眩晕专诊+VM筛查稳量上移；朱伟VM筛查+跨科(神内→ENT)转诊；刘迎梅重启痛晕专诊模块+打标签激活；清单扩容新增1-2位ENT眩晕/VM KOL(见客户名单末行)，建VM筛查流程(ICHD-3)，严守Do/Don't(仅急性期、75mg按需、不超适应症、GCMA审批)。5.KOL金字塔与244扩容(补④)：244标签9→≥18/23(14位缺失优先补全)；代言(Ambassador)由2→3人(赵中/付建忠/冯红选)；倡导(Advocator)由2→≥6人(付建忠/冯红选/王媚瑕/邓朋/冯倩/邓邦鱼)；讲者TTT+GD会+区域会放大peer影响。</t>
+          <t>1.VM客户识别2.新A客户门诊量转诊建设3.老A圈层活动，引流患者4.B类客户明诊断5.大D类客户DOT延长</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1.9月协助付建忠维持头痛专诊8/月满负荷，冯红选/王媚瑕专诊4→8扩容，赵中申请'头痛/情绪共病'专病门诊并增号源，门诊地图/互联网医院完成专诊标注。2.每次专诊/出诊前递送偏头痛预防治疗指南，月发作≥2次患者按指南评估预防需求，头部持续新增全程管理患者。3.9月以GD会开展1次科室'偏头痛全程管理'病例讨论会，付建忠/王媚瑕主讲，覆盖神内+耳鼻喉目标客户，会后1周未到场一对一补访。4.邓邦鱼推动设眩晕专诊+建VM筛查流程(ICHD-3)，朱伟/刘迎梅完善VM标签+跨科转诊，严守VM推广Do/Don't。5.9位沉睡脑血管B类(周华等)分批补全244标签+出诊简介标签(STEP1打标签)，按'科室会批量/一对一先行/区域会预热/开专病门诊/增模块号源'差异化杠杆破冰，推动不管不治→阶梯。6.吴冠会(24/月)优先PSR电话/微信随访既往患者重建信心并补244标签，王薇/沈蓉/沈明强补244标签撬动高门诊量；每次拜访带1典型病例强化规范治疗。7.清单扩容：摸排耳鼻喉眩晕/头痛亚专业新增1-2位目标医生(客户名单末行示意)，纳入244标签与VM专项管理。</t>
+          <t>1.9月协助付建忠维持头痛专诊8/月满负荷，冯红选/王媚瑕专诊4→8扩容，赵中申请'头痛/情绪共病'专病门诊并增号源，门诊地图/互联网医院完成专诊标注。2.每次专诊/出诊前递送偏头痛预防治疗指南，月发作≥2次患者按指南评估预防需求，头部持续新增全程管理患者。3.9月以GD会开展1次科室'偏头痛全程管理'病例讨论会，付建忠/王媚瑕主讲，覆盖神内+耳鼻喉目标客户，会后1周未到场一对一补访。
+4.邓邦鱼推动设眩晕专诊+建VM筛查流程(ICHD-3)，朱伟/刘迎梅完善VM标签+跨科转诊，严守VM推广Do/Don't。5.9位沉睡脑血管B类(周华等)分批补全244标签+出诊简介标签(STEP1打标签)，按'科室会批量/一对一先行/区域会预热/开专病门诊/增模块号源'差异化杠杆破冰，推动不管不治→阶梯。6.吴冠会(24/月)优先PSR电话/微信随访既往患者重建信心并补244标签，王薇/沈蓉/沈明强补244标签撬动高门诊量；每次拜访带1典型病例强化规范治疗。7.清单扩容：摸排耳鼻喉眩晕/头痛亚专业新增1-2位目标医生(客户名单末行示意)，纳入244标签与VM专项管理。</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
           <t>1.偏头痛预防治疗最新指南/共识、前庭性偏头痛ICHD-3诊断标准、抑郁焦虑-偏头痛共病文献、瑞美吉泮循证包(2小时无痛率/安全性)。2.9月科室'偏头痛全程管理'GD会名额、GCMA审批幻灯片、讲者TTT赋能(付建忠/王媚瑕/冯红选)。3.门诊地图/互联网医院专诊标注资源、专病门诊/加号审批协调。4.244标签系统录入支持、出诊简介标签优化工具(STEP1)、VM筛查表/VM质控共识/眩晕专诊建设工具包(话术单页、VM宣教单页、随访工具、眩晕日记模板)。5.PSR对既往处方患者电话/微信随访模板+疗效反馈收集、零新处方医生入门培训包、首方信心建立工具、同伴经验分享。6.上级医院头痛中心会诊/转诊资源、区域头痛学科建设平台学术活动名额、ENT眩晕/VM专项学术资源。</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>深挖A识别BC引领D</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>GD1 LB2</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3413,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>384</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3422,12 +3448,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3437,7 +3463,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -3472,84 +3498,84 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>500+</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>500+</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AW13" t="inlineStr">
         <is>
           <t>0</t>
@@ -3562,22 +3588,26 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>升级AB客户观念，扩大cd客户面</t>
+          <t>升级AC客户观念，扩大BD客户
+面</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>AB客户强客情，学术观念升级，cd客户科室会议覆盖，学术观念共识</t>
+          <t>1：Ac客户强客情，学术观念升级（重点客户：汪敬业 高建国胡雅娟章娟娟 赵益制定一人一策促进治痛治晕观念升级）2：bd（张龙，赵丽，朱本藩等）客户科室会议覆盖，学术观念共识，加速从破冰到倡导提升3：急诊科全门诊覆
+盖，协助瑞美急性眩晕患者归拢4:神经内科做定期主题GD会开展，培养中青年医生治痛理念/偏头痛共病/瑞美治痛机制区隔</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>A客户通过系列会议打造专家圈层B客户强客情，以张龙主任牵头，打造专家圈 CD客户 拓展耳鼻喉科 疼痛科，开展科室会议，拓展客户面</t>
+          <t>1：A客户通过系列会议打造专家圈层（覆盖专家：汪敬业 王玉 胡雅娟 章娟娟 ）2：B客户强客情，以张龙主任牵头，打造专家圈（张龙  燕晓翔  ）3：C客户 拓展耳鼻喉科 疼痛科，开展科室会，耳鼻喉客户面目前4位专家（赵益   王琴  李亦凡  余崇仙  ）以赵益主任牵头，收集优质病例，协助随访，带动科室老师提升瑞美治晕观念  4：D客户 为疼痛科，急诊科，通过强客情以及科研推动，由目前4位破冰客户（赵丽  朱本藩  杨文蓓  刘茵 ）9月升级为重复客户活跃客户，破冰客户数由4升级至
+8。9月安医目标：9月中旬tth220  9月下旬tth2609月南区（高新）目标 9月中旬48  9月下旬72</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1：安徽头痛小组系列会议2：脑血管主题系列会议</t>
+          <t>1：王玉院长牵头安徽头痛眩晕协作组系列会议，覆盖AC客户2：张龙脑血管主题系列会议覆盖B客户3：科室会议 vm相关三方会议覆盖耳鼻喉C客户  4：科室会议LB会议覆盖疼痛科，急诊科D客户（lb会议一场疼痛科覆盖，gd一场疼痛科 一场神经内科神经内科
+两场急诊科）</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3670,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3893,7 +3923,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -4068,27 +4098,34 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>诊断率较低，B\C采用阶梯疗法
-科内对于头痛头晕不是特别重视</t>
+          <t>1.客户面明显不足，无C类客户
+2.头痛眩晕专科不受重视，限制发展
+3.中药价格昂贵且长期吃副作用大，服药不方便，依从性弱导致治疗失败、患者流失</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>定期覆盖科主任，提高其头痛眩晕观念得到科主任支持，助力A\C发展
-协助相关研究，提高科室知名度</t>
+          <t>1.科内支持：得到科主任支持头痛头晕亚专业发展
+2.渠道问题：探寻有无进院临采可能
+3.客户面：B、C类客户每月 2场GD覆盖做到全覆盖
+4.专病门诊增加
+5.由纯中药-中西医结合诊断治疗</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>通过协助入组研究延长DOT
-刘凯鸣、张甦琳影响PPPD和VM时间界限，提高共病诊断率</t>
+          <t>1.定期覆盖科主任，提高其头痛眩晕观念得到科主任支持，助力A\C发展
+2.利用国家级/省级会议提高科室中西医结合治疗头痛头晕知名度
+3.每月2场GD会议，1场LB会议覆盖所有B、C类客户，拓宽处方面
+4.继续推动大A客户专家门诊-专病门诊转换，提高患者归拢率
+5.目标中医客户达到100%推荐介绍CGRP药物优势由纯中医方案-中西医结合方案，增加医院特色助力偏头痛治疗</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>江苏省眩晕学会任职
-医学部协助完成VM研究
-全国眩晕平台授课提高知名度</t>
+          <t>1.江苏省眩晕学会管理任职
+2.医学部协助共访
+3.全国眩晕平台/NHC项目授课提高知名度</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4188,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>280</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -4236,12 +4273,12 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -4404,7 +4441,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>188</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4686,7 +4723,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>196</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4962,7 +4999,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>212</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -5210,7 +5247,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>230</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -5463,7 +5500,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>176</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -5503,52 +5540,52 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -5724,7 +5761,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5764,7 +5801,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -5774,7 +5811,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -5809,7 +5846,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -6231,7 +6268,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>208</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -6728,7 +6765,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -6763,7 +6800,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -6818,14 +6855,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>0</t>
@@ -6848,7 +6885,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>300</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -6866,6 +6903,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>12</t>
@@ -6908,12 +6950,19 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>围绕安徽省头痛小组建设发展，积极拓展科室头痛人员观念，眩晕中心建设安徽省的标杆，打造全省到全国的影响力</t>
+          <t>"A类头痛领域：依托安徽省头痛小组，聚焦桂韦、王梓，攻坚头痛诊断率与推荐率，搭建科室人才梯队。
+B类脑血管病：以程昭昭主任为核心，开展全省学术活动，升级区域诊疗及用药理念，扩大学术影响力。
+C类耳鼻喉眩晕中心：借力孙敬武院长支持，由潘春晨主任牵头建设省级眩晕中心，立足现有2个眩晕专诊，提升VM诊断率、规范患者归拢；完成刘晓薇、王俊观念破冰，推动临床实践转变。
+D类新科室拓展：主攻疼痛科孔令锁主任，同步深耕急诊科，突破急诊用药场景，完成科室覆盖。"
+。</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>头痛专向会议覆盖，以安徽省眩晕中心建设开展VM的专向治疗标准和观念</t>
+          <t>A类客户（头痛）：桂韦争取全省及全国头痛学术会议资源月均2场，实现客户参会覆盖。王梓LB科室会议
+​B类客户（脑血管病）：程昭昭支持线上、线下PO脑血管共病专题会议，辐射全省B类客户。王国平主任主席三方
+​C类客户（眩晕中心）：潘春晨搭建眩晕中青年学术交流平台，提供全国会议交流机会，助力省级眩晕中心建设。王俊三方会议讨论
+​ D类客户（急诊、疼痛科）：重点做好客情深耕，提供全国学术会议参会邀约，赋能科室学习提升。</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7273,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>245</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -8261,7 +8310,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -8301,22 +8350,22 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -8346,7 +8395,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -8587,7 +8636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z554"/>
+  <dimension ref="A1:Z613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8829,7 +8878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>72</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -10983,7 +11032,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>168</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -11491,7 +11540,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -15047,7 +15096,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -16683,7 +16732,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>508</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -16810,7 +16859,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>444</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -18969,7 +19018,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -21890,7 +21939,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -24176,7 +24225,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>104</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -24313,7 +24362,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>72</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -26207,7 +26256,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -26334,7 +26383,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -26588,7 +26637,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>96</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -26842,7 +26891,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -29255,7 +29304,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
@@ -31414,7 +31463,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
@@ -31541,7 +31590,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -34589,7 +34638,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
@@ -34843,7 +34892,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U208" t="inlineStr">
@@ -35732,7 +35781,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>248</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
@@ -35753,21 +35802,21 @@
       <c r="X215" t="inlineStr">
         <is>
           <t>标签/专诊/号源：门诊简介无标签，可通过标签完善与专诊提高归拢率
-聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别，传递足量足疗程观念，以及患者管理的必要性</t>
+聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别，传递足量足疗程观念</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
         <is>
           <t>1每周2次深访，【专诊号源/标签】协同门诊推动开设耳鼻喉科眩晕专诊或增加专诊，增加标签，扩充号源以承接更多患者。
-2聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
+2聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录变化以强化观念。
 邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，带动眩晕/耳鼻喉组内观念</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
           <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
+患者教育材料与治痛管理工具包（随访表、记录卡），支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与指南，专家共识参与，学会加入</t>
         </is>
       </c>
     </row>
@@ -35884,21 +35933,19 @@
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>1，目标升级至治痛管理——全方位认可疗效/频率/安全，将中高频患者治痛管理周期延长至6个月，实现疾病病程逆转，推动低频首选瑞美吉泮急性治疗、中高频启动治痛管理。2借助头痛中心申办成功，公众号宣传，归拢更多的偏头痛患者</t>
+          <t>1，目标升级至治痛管理——全方位认可疗效/频率/安全，将中高频患者治痛管理周期延长至6个月，实现疾病病程逆转，推动低频首选瑞美吉泮急性治疗、中高频启动治痛管理。2借助头痛中心申报成功，公众号宣传，归拢更多的偏头痛患者，分层治疗方案</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
         <is>
           <t>开展2次1对1学术拜访/周：全方位认可疗效/频率/安全，将中高频患者治痛管理周期延长至6个月，实现疾病病程逆转；用真实世界证据与指南传递瑞美吉泮疗效/频率/安全三位一体价值。
-聚焦偏头痛"识别-诊断-治疗"路径：重点识别中高频发作(≥4天/月)及伴心脑血管风险的偏头痛患者，推动低频首选瑞美吉泮急性治疗、中高频启动治痛管理；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，带动神经内科头痛专业组内观念传递。</t>
+聚焦偏头痛"识别-诊断-治疗"路径：重点识别中高频发作(≥4天/月)及伴心脑血管风险的偏头痛患者，推动低频首选瑞美吉泮急性治疗、中高频启动治痛管理；对患者启动治痛管理随访，记录头痛日记以强化观念。
+邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，带动神经内科头痛专业组内观念传递</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>协同拜访资源与区域学术会议/沙龙名额/LB
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，提高影响力</t>
+          <t>协同拜访资源与区域学术会议/全国会议参会名额/LB/省级以上学会名额/提高区域影响力</t>
         </is>
       </c>
     </row>
@@ -36015,7 +36062,7 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>1分层治疗方案的传递，必赢画像中高频患者必须足量足疗程治疗3-6个月，可逆转疾病进展 2 传递VM五大形态，对于PVM患者，首选瑞美3外部最新治疗方案的传递</t>
+          <t>1分层治疗方案的传递，必赢画像中高频患者必须足量足疗程治疗3-6个月，可逆转疾病进展 2 传递VM五大形态，对于PVM患者，首选瑞美，外部最新治疗方案的传递</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -36025,9 +36072,9 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>PIM CALL/LB
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，提高影响力</t>
+          <t>协防/LB
+患者教育材料与治痛管理工具包
+城市会/区域会讲者平台/全国参会名额</t>
         </is>
       </c>
     </row>
@@ -36144,8 +36191,7 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>强化对疗效/频率/安全中其余方面的认可，将管理周期从1-2个月延长至3个月治痛管理，降低患者每月头痛天数(MMD)。
-聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患者，此类人群优先选用瑞美吉泮。</t>
+          <t>1强化对疗效/频率/安全中其余方面的认可，将管理周期从1-2个月延长至3个月治痛管理，降低患者每月头痛天数(MMD)。2传递分层治疗方案，中高频，3-6个月治痛管理，可逆转疾病进展</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -36156,8 +36202,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>DM/RM/RPM协同拜访,高质量会议邀请。
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。</t>
+          <t>DM/RM/RPM协同拜访,高质量会议讲者邀请。</t>
         </is>
       </c>
     </row>
@@ -36274,18 +36319,674 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
+          <t>强化对疗效/频率/安全中其余方面的认可，将管理周期从1个月延长至3-6个月治晕治痛管理
+诊疗路径识别：聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别 ，耳石症反复复位无效的患者，可使用CGRP靶向治疗药物治疗，后续正反馈传递，加强信心</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>诊前拜访，聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
+2邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，圈层搭建</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>LB
+城市会/区域会讲者平台，学会任职</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>曹茂红</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者以及，睡眠障碍合并偏头痛患者</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>增加拜访频率/周/1次传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
+【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访
+安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>DM/RM/RPM协同拜访资源与区域学术会议名额，三方会议
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>樊兴娟</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>脑血管</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮进行治疗，而非从NSAIDs/曲坦起步。
+标签：通过标签完善提升归拢率
+诊疗路径识别：聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患，优先选用瑞美吉泮。</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>拜访频率1次/周，传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
+【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>DM/RM/RPM协同拜访,高质量会议邀请。
+患者教育材料与治痛管理工具包，传递正反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>倪耀辉</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>脑血管</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者使用瑞美治疗方案，以及传递传统治疗药物的副作用，首选瑞美</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步；用真实世界证据与指南传递瑞美吉泮疗效/频率/安全三位一体价值。
+【专诊号源】协同门诊推动开设神经内科头痛/眩晕专诊或增加专诊单元，扩充号源以承接更多患者。
+【标签体系】提升医生在院内系统的偏头痛/眩晕标签识别与检索可见度。
+【诊疗路径】聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患者，此类人群优先选用瑞美吉泮；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+【学术触达】安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
+患者教育材料与治痛管理工具包，支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>成亚琴</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>脑血管</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮进行治疗，而非从NSAIDs/曲坦起步。
+标签：通过标签完善提升归拢率
+诊疗路径识别：聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患，优先选用瑞美吉泮。</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>前置拜访，诊后复盘。传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
+【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>DM/RM/RPM协同拜访,高质量会议邀请。
+患者教育材料与治痛管理工具包，传递正反馈</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>胡松群</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>耳鼻喉科</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>头晕/眩晕</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
           <t>强化对疗效/频率/安全中其余方面的认可，将管理周期从1个月延长至3个月治晕管理
 诊疗路径识别：聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别 ，前庭性偏头痛患者足量足疗程治疗后，正反馈传递</t>
         </is>
       </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>。
-1诊前拜访，聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>1前置拜访，诊后复盘，聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
 2邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，圈层搭建</t>
         </is>
       </c>
-      <c r="Z219" t="inlineStr">
+      <c r="Z224" t="inlineStr">
         <is>
           <t>PIM CALL/LB
 患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
@@ -36293,666 +36994,6 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>曹茂红</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>神经内科</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>增加拜访频率/周/1次传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>樊兴娟</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>神经内科</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>脑血管</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮进行治疗，而非从NSAIDs/曲坦起步。
-标签：通过标签完善提升归拢率
-诊疗路径识别：聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患，优先选用瑞美吉泮。</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>拜访频率1次/周，传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>DM/RM/RPM协同拜访,高质量会议邀请。
-患者教育材料与治痛管理工具包，传递正反馈</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>倪耀辉</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>神经内科</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>脑血管</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>拜访1次/周，开展1对1学术拜访：传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步；用真实世界证据与指南传递瑞美吉泮疗效/频率/安全三位一体价值。
-【专诊号源】协同门诊推动开设神经内科头痛/眩晕专诊或增加专诊单元，扩充号源以承接更多患者。
-【标签体系】推动建立244标签，提升医生在院内系统的偏头痛/眩晕标签识别与检索可见度。
-【诊疗路径】聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患者，此类人群优先选用瑞美吉泮；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-【学术触达】安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>成亚琴</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>神经内科</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>脑血管</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮进行治疗，而非从NSAIDs/曲坦起步。
-标签：通过标签完善提升归拢率
-诊疗路径识别：聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患，优先选用瑞美吉泮。</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>前置拜访，诊后复盘。传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>DM/RM/RPM协同拜访,高质量会议邀请。
-患者教育材料与治痛管理工具包，传递正反馈</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>胡松群</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>耳鼻喉科</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>头晕/眩晕</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>短期治痛（Advocator）</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>强化对疗效/频率/安全中其余方面的认可，将管理周期从1个月延长至3个月治晕管理
-诊疗路径识别：聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别 ，前庭性偏头痛患者足量足疗程治疗后，正反馈传递</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>。
-1前置拜访，诊后复盘，聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
-2邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，圈层搭建</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>PIM CALL/LB
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，学会任职</t>
-        </is>
-      </c>
-    </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
@@ -37066,1186 +37107,10 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
+          <t>从『不管不治』破冰，建立CGRP与偏头痛诊疗关联，进入阶梯治疗（Tryer）。挂号系统显示其无专病门诊设置、月均8个半天非专诊（无专诊模块），tth目前基本为0（还没起量）。机会点：依托神经内科头痛/眩晕门诊推动开设专病门诊/增加号源，扩大患者触达；先把244标签和出诊简介里的头痛/眩晕标签补全，提升系统识别度；在脑血管门诊里识别偏头痛共病/血管风险人群(卒中风险/PFO/脑白质病变等)，这类人优先用瑞美吉泮；tth还基本是0，从0到1先把关联建起来，小步起量冲9月12片。</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
-        <is>
-          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>协同拜访资源与区域学术会议/沙龙名额
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>张元媛</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>神经内科</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>脑血管</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>张云峰</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>神经内科</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>脑血管</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>区域学术会议名额，LB召开
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>殷勇</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>耳鼻喉科</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>头晕/眩晕</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V228" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W228" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="X228" t="inlineStr">
-        <is>
-          <t>强化对疗效/频率/安全中其余方面的认可，将管理周期从1个月延长至3个月治晕管理
-诊疗路径识别：聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别 ，前庭性偏头痛患者足量足疗程治疗后，正反馈传递</t>
-        </is>
-      </c>
-      <c r="Y228" t="inlineStr">
-        <is>
-          <t>。
-1聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
-2邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，圈层搭建</t>
-        </is>
-      </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>PIM CALL/LB
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，学会任职</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>蒋锐</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>手术评估无需手术，高频/中频患者，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。术后出院患者，可出院带药，预防急性发作</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>每次诊前拜访，手术评估无需手术，高频/中频患者，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。术后出院患者，可出院带药，预防急性发作</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>PIM CALL/LB
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，学会任职，提高影响力</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>缪秀华</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>疼痛</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>传递目前疼痛科治疗现状，以及外部专家使用方案。分层治疗方案传递，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>每次诊前拜访，手术评估无需手术，高频/中频患者，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。术后出院患者，可出院带药，预防急性发作</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>PIM CALL/LB
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，学会任职，提高影响力</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>李晓飞</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>区域学术会议名额，LB召开
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>郑冬冬</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
-【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
-安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>区域学术会议名额，LB召开
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>刘浩</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>耳鼻喉科</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>头晕/眩晕</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>标签/专诊/号源：门诊简介无标签，可通过标签完善与专诊提高归拢率
-聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别，传递足量足疗程观念，以及患者管理的必要性</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>1每周2次深访，【专诊号源/标签】协同门诊推动开设耳鼻喉科眩晕专诊或增加专诊，增加标签，扩充号源以承接更多患者。
-2聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
-邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，带动眩晕/耳鼻喉组内观念</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
-患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
-标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>南通大学附属医院</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>顾晓苏</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>神经内科</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>脑血管</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>无专诊设置</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>不管不治（Freezer）</t>
-        </is>
-      </c>
-      <c r="V234" t="inlineStr">
-        <is>
-          <t>阶梯治疗（Tryer）</t>
-        </is>
-      </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>从『不管不治』破冰，建立CGRP与偏头痛诊疗关联，进入阶梯治疗（Tryer）。挂号系统显示其无专病门诊设置、月均8个半天非专诊（无专诊模块），tth目前基本为0（还没起量）。机会点：依托神经内科头痛/眩晕门诊推动开设专病门诊/增加号源，扩大患者触达；先把244标签和出诊简介里的头痛/眩晕标签补全，提升系统识别度；在脑血管门诊里识别偏头痛共病/血管风险人群(卒中风险/PFO/脑白质病变等)，这类人优先用瑞美吉泮；tth还基本是0，从0到1先把关联建起来，小步起量冲9月12片。</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
         <is>
           <t>1) 每月1-2次破冰拜访，传递CGRP受体拮抗剂与偏头痛规范诊疗的关联，逐步提升观念层级；
 2) 协同院方/科室推动开设神经内科头痛/眩晕专病门诊或扩容号源，多接患者；
@@ -38254,7 +37119,7 @@
 5) 安排参加科室会/城市沙龙，借KOL观念辐射慢慢做起来；</t>
         </is>
       </c>
-      <c r="Z234" t="inlineStr">
+      <c r="Z225" t="inlineStr">
         <is>
           <t>医学部审批通过的瑞美吉泮学术资料/幻灯（疗效·频率·安全·心脑血管风险定位）；
 专诊开设与号源扩容的院方协调资源，以及244标签/出诊简介标签的系统录入支持；
@@ -38264,130 +37129,130 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>南通大学附属医院</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>赵映红</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>张元媛</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
         <is>
           <t>神经内科</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>脑血管</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
         <is>
           <t>无专诊设置</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr">
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U235" t="inlineStr">
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
         <is>
           <t>不管不治（Freezer）</t>
         </is>
       </c>
-      <c r="V235" t="inlineStr">
+      <c r="V226" t="inlineStr">
         <is>
           <t>阶梯治疗（Tryer）</t>
         </is>
       </c>
-      <c r="W235" t="inlineStr">
+      <c r="W226" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="X235" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
         </is>
       </c>
-      <c r="Y235" t="inlineStr">
+      <c r="Y226" t="inlineStr">
         <is>
           <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
 【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
 安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr">
+      <c r="Z226" t="inlineStr">
         <is>
           <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
 患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
@@ -38395,123 +37260,517 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>南通大学附属医院</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>CORE</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>秦毅彬</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>疼痛科</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>张云峰</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>脑血管</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
+【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>区域学术会议名额，LB召开
+患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>殷勇</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>耳鼻喉科</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>头晕/眩晕</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>止痛优选（Repeater）</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>强化对疗效/频率/安全中其余方面的认可，将管理周期从1个月延长至3个月治晕管理
+诊疗路径识别：聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别 ，前庭性偏头痛患者足量足疗程治疗后，正反馈传递。添加标签</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>1聚焦前庭性偏头痛(反复眩晕+头痛史)的识别，与BPPV/梅尼埃病鉴别；对前庭性偏头痛患者定位瑞美吉泮在急性与频率管理中的价值；对患者启动治痛管理随访，记录MMD变化以强化观念。
+2邀请参与区域学术会议/科室沙龙并争取讲者/病例分享机会，圈层搭建</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>PIM CALL/LB
+城市会/区域会讲者平台与青年医生带教，学会任职</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>蒋锐</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>手术评估无需手术，高频/中频患者，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。术后出院患者，可出院带药，预防急性发作</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>每次诊前拜访，手术评估无需手术，高频/中频患者，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。术后出院患者，可出院带药，预防急性发作</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>PIM CALL/LB
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，学会任职，提高影响力</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>缪秀华</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
         <is>
           <t>疼痛</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="I230" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>疼痛专诊</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M236" t="inlineStr">
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V236" t="inlineStr">
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
         <is>
           <t>阶梯治疗（Tryer）</t>
         </is>
       </c>
-      <c r="W236" t="inlineStr">
+      <c r="W230" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="X236" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>传递目前疼痛科治疗现状，以及外部专家使用方案。分层治疗方案传递，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。</t>
         </is>
       </c>
-      <c r="Y236" t="inlineStr">
+      <c r="Y230" t="inlineStr">
         <is>
           <t>每次诊前拜访，手术评估无需手术，高频/中频患者，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。术后出院患者，可出院带药，预防急性发作</t>
         </is>
       </c>
-      <c r="Z236" t="inlineStr">
+      <c r="Z230" t="inlineStr">
         <is>
           <t>PIM CALL/LB
 患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
@@ -38519,6 +37778,791 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>李晓飞</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
+【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>区域学术会议名额，LB召开
+患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>郑冬冬</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
+【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>区域学术会议名额，LB召开
+患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>刘浩</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>耳鼻喉科</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>头晕/眩晕</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者以及偏头痛合并心血管疾病的患者，偏头痛药物使用的禁忌，传递足量足疗程治疗方案</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖。
+【诊疗路径】建立CGRP受体拮抗剂与偏头痛/头痛诊疗的有效关联，从零搭建相关患者的识别与处理意识；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>区域学术会议名额，LB召开
+患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>顾晓苏</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>脑血管</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者使用瑞美治疗方案，以及传递传统治疗药物的副作用，首选瑞美</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>1) 每月1-2次破冰拜访，传递CGRP受体拮抗剂与偏头痛规范诊疗的关联，逐步提升观念层级；
+2) 协同院方/科室推动开设神经内科头痛/眩晕专病门诊或扩容号源，多接患者；
+3) 推动补全244标签与出诊简介中的头痛/眩晕标签，让系统能检索到、患者能挂对号；
+4) 在脑血管门诊里识别偏头痛共病/血管风险人群(卒中风险/PFO/脑白质病变等)，这类人优先用瑞美吉泮；对适合的患者启动治痛管理随访，用MMD变化说话；
+5) 安排参加科室会/城市沙龙，借KOL观念辐射慢慢做起来；</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>医学部审批通过的瑞美吉泮学术资料/幻灯（疗效·频率·安全·心脑血管风险定位）；
+专诊开设与号源扩容的院方协调资源，以及244标签/出诊简介标签的系统录入支持；
+MICS/DM协同拜访资源，区域学术会议/沙龙名额（含讲者、交通、会务）；
+患者教育材料和治痛管理工具包（随访表、MMD记录卡）；
+基础学术资料与新人破冰拜访带教支持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>赵映红</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>神经内科</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>脑血管</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>无专诊设置</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>不管不治（Freezer）</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>分层治疗方案传递，对中高频患者使用瑞美治疗方案，以及传递传统治疗药物的副作用，首选瑞美</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步；用真实世界证据与指南传递瑞美吉泮疗效/频率/安全三位一体价值。
+【专诊号源】协同门诊推动开设神经内科头痛/眩晕专诊或增加专诊单元，扩充号源以承接更多患者。
+【标签体系】提升医生在院内系统的偏头痛/眩晕标签识别与检索可见度。
+【诊疗路径】聚焦偏头痛共病及脑血管风险人群：识别伴心脑血管基础疾病/卒中风险/PFO/脑白质病变的偏头痛患者，此类人群优先选用瑞美吉泮；对适合患者启动治痛管理随访，记录MMD变化以强化观念。
+【学术触达】安排参加科室会/城市沙龙，借助区域KOL观念辐射逐步实现从0到1的开发。</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>DM/RM/RPM协同拜访资源与区域学术会议名额。
+患者教育材料与治痛管理工具包，支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教支</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>南通大学附属医院</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>秦毅彬</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>疼痛科</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>疼痛</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>疼痛专诊</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>阶梯治疗（Tryer）</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>传递目前疼痛科治疗现状，以及外部专家使用方案。分层治疗方案传递，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>每次诊前拜访，手术评估无需手术，高频/中频患者，使用瑞美足量足疗程治疗3-6月，可逆转疾病进展。术后出院患者，可出院带药，预防急性发作</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>PIM CALL/LB
+患者教育材料与治痛管理工具包（随访表、MMD记录卡），支撑长期管理落地。
+标杆医生培育资源：城市会/区域会讲者平台与青年医生带教，学会任职，提高影响力</t>
+        </is>
+      </c>
+    </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
@@ -38612,7 +38656,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>324</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
@@ -38767,11 +38811,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>【分层治疗】传递分层治疗方案：针对中高频患者及偏头痛合并心血管疾病的患者，明确药物使用禁忌；同时传递足量足疗程的治疗方案。</t>
-        </is>
-      </c>
       <c r="Y238" t="inlineStr">
         <is>
           <t>1) 传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖；
@@ -38896,12 +38935,6 @@
       <c r="W239" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>1A类客户但观念仅处于阶梯治疗层级，传递分层治疗观念，中高频患者治疗3-6个月可逆转疾病进展，加速观念提升至止痛优选乃至治痛管理；
-2.头痛专诊患者中高频发作（≥4天/月）比例高可推动全程管理模式；</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
@@ -39033,11 +39066,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>【分层治疗】传递分层治疗方案：针对中高频患者及偏头痛合并心血管疾病的患者，明确药物使用禁忌；同时传递足量足疗程的治疗方案。</t>
-        </is>
-      </c>
       <c r="Y240" t="inlineStr">
         <is>
           <t>1) 传递心脑血管风险偏头痛患者的识别方法，使其认识到此类患者应优先选用瑞美吉泮（CGRP受体拮抗剂）进行急性治疗，而非一律从NSAIDs/曲坦起步，并扩大适应证内患者覆盖；
@@ -39164,12 +39192,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>【标签/专诊/号源】门诊简介暂无标签，可通过完善标签、增设或扩容专诊来提高患者归拢率。
-【诊疗观念】聚焦前庭性偏头痛（反复眩晕+头痛史）的识别，与BPPV、梅尼埃病做好鉴别；传递足量足疗程观念，并强调患者长期管理的必要性。</t>
-        </is>
-      </c>
       <c r="Y241" t="inlineStr">
         <is>
           <t>1) 每周2次深访，【专诊号源/标签】协同门诊推动开设耳鼻喉科眩晕专诊或增加专诊，补全标签、扩充号源以承接更多患者；
@@ -39294,12 +39316,6 @@
       <c r="W242" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>1.从"不管不治"向"阶梯治疗"破冰，传递分层治疗观念，中高频患者治疗3-6个月可逆转疾病进展，加速观念提升至止痛优选乃至治痛管理；
-2.伴心脑血管风险的偏头痛患者中，NSAIDs/曲坦类存在禁忌，CGRP受体拮抗剂具有差异化优势。</t>
         </is>
       </c>
       <c r="Y242" t="inlineStr">
@@ -39432,12 +39448,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>【标签/专诊/号源】门诊简介暂无标签，可通过完善标签、增设或扩容专诊来提高患者归拢率。
-【诊疗观念】聚焦前庭性偏头痛（反复眩晕+头痛史）的识别，与BPPV、梅尼埃病做好鉴别；传递足量足疗程观念，并强调患者长期管理的必要性。</t>
-        </is>
-      </c>
       <c r="Y243" t="inlineStr">
         <is>
           <t>1) 每周2次深访，【专诊号源/标签】协同门诊推动开设耳鼻喉科眩晕专诊或增加专诊，补全标签、扩充号源以承接更多患者；
@@ -40366,11 +40376,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>CDSS海报的投放；PSR跟诊引导；清秀主任门诊跟诊学习</t>
-        </is>
-      </c>
       <c r="Y250" t="inlineStr">
         <is>
           <t>1.每周复盘CDSS扫码入组情况；2.出诊时间不固定，解决方案，患者群内提前预告下周出诊时间；3.跟诊学习，进一步提升诊断及话术，寻找突破思路，完善诊疗路径</t>
@@ -40493,11 +40498,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>流调投放；患者定期随访管理</t>
-        </is>
-      </c>
       <c r="Y251" t="inlineStr">
         <is>
           <t>1.通过流调融动主任进阶；2.通过患者随访管理，积累病例，增强用药信心</t>
@@ -40620,11 +40620,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>已预约小圈子宴请；有较好的合作意愿度、配合度</t>
-        </is>
-      </c>
       <c r="Y252" t="inlineStr">
         <is>
           <t>1.通过小圈子宴请，加深客情及拓圈；2.邀请参加会议，做好资源覆盖</t>
@@ -40747,11 +40742,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>门诊出诊天数高，有处方经验，但是观念较为保守，认为价格高，服用托吡酯可解决大部分患者问题</t>
-        </is>
-      </c>
       <c r="Y253" t="inlineStr">
         <is>
           <t>小圈子宴请，加强覆盖及拜访频率；Q4重点客户覆盖，提升治痛治晕观念</t>
@@ -40874,11 +40864,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>每周出眩晕专诊，门诊患者质量较高</t>
-        </is>
-      </c>
       <c r="Y254" t="inlineStr">
         <is>
           <t>Q4通过会议覆盖提升产品认可度及观念，高频拜访融动</t>
@@ -41001,11 +40986,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>具备一定的用药经验，但治痛理念还需持续融动提升</t>
-        </is>
-      </c>
       <c r="Y255" t="inlineStr">
         <is>
           <t>小圈子宴请邀约，Q4会议覆盖</t>
@@ -41110,7 +41090,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
@@ -41126,11 +41106,6 @@
       <c r="W256" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>治痛治晕理念较好，有处方经验，非常认可CGRP机制，但主攻方向为睡眠障碍，表示无法兼顾头痛</t>
         </is>
       </c>
       <c r="Y256" t="inlineStr">
@@ -41255,11 +41230,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>已成功破冰，且获得病例正反馈</t>
-        </is>
-      </c>
       <c r="Y257" t="inlineStr">
         <is>
           <t>持续跟进，抑郁焦虑共病偏头痛患者画像，参加会议讨论，增强用药信心</t>
@@ -41382,11 +41352,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>对于PFO有较多患者，且深耕PFO研究；参加9月份PFO会议</t>
-        </is>
-      </c>
       <c r="Y258" t="inlineStr">
         <is>
           <t>对于PFO患者，可进一步融动，寻找生意机会</t>
@@ -41509,11 +41474,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>脑血管病方向，门诊头痛患者优先选用院内产品，自费且院外产品拒绝合作</t>
-        </is>
-      </c>
       <c r="Y259" t="inlineStr">
         <is>
           <t>利用病例正反馈及王琨主任，融动破冰</t>
@@ -41636,11 +41596,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>朱晓宁主任学会共同发起，借助学会及流调加强大客户管理，沟通医院临采提单</t>
-        </is>
-      </c>
       <c r="Y260" t="inlineStr">
         <is>
           <t>对流调及学会事宜深入沟通，客情维护</t>
@@ -41763,11 +41718,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>已参加线下会议，对于产品机制较为认可，但在诊断方面存在提升空间</t>
-        </is>
-      </c>
       <c r="Y261" t="inlineStr">
         <is>
           <t>目前有锁定患者，跟进破冰后，持续融动</t>
@@ -42266,16 +42216,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>自身是偏头痛患者，对于产品疗效很认可</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>病房主任，通过GD会议覆盖</t>
-        </is>
-      </c>
       <c r="Z265" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -42393,16 +42333,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>门诊偏头痛患者较少，既往无处方经验；但合作意愿度较高</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>夜访跟进，明确患者画像，利用病例正反馈，融动处方破冰</t>
-        </is>
-      </c>
       <c r="Z266" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -42520,17 +42450,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>1、参加线上PO会议，同步其他区域优质病例，传递需要尽早治疗，足疗程治疗
-2、每周三拜访复盘近期处方患者，收集足量足疗程病例3、每月一次家访，增强客情</t>
-        </is>
-      </c>
       <c r="Z267" t="inlineStr">
         <is>
           <t>po会1季度1-2场，GD会议覆盖</t>
@@ -42648,16 +42567,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>增加头痛专诊量，提升偏头痛诊断率，提高患者归拢率，增加门诊标签</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>1、开展GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
-        </is>
-      </c>
       <c r="Z268" t="inlineStr">
         <is>
           <t>三方会1季度1-2场，GD会议覆盖</t>
@@ -42775,16 +42684,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>增加头痛专诊量，提升偏头痛诊断率，提高患者归拢率，增加门诊标签</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
-        </is>
-      </c>
       <c r="Z269" t="inlineStr">
         <is>
           <t>三方会1季度1-2场，GD会议覆盖</t>
@@ -42902,16 +42801,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>增加头痛专诊量，提升偏头痛诊断率，提高患者归拢率，增加门诊标签</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
-        </is>
-      </c>
       <c r="Z270" t="inlineStr">
         <is>
           <t>GD会议覆盖</t>
@@ -43029,16 +42918,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
-        </is>
-      </c>
       <c r="Z271" t="inlineStr">
         <is>
           <t>三方会1季度1-2场，GD会议覆盖</t>
@@ -43156,11 +43035,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
       <c r="Y272" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -43283,11 +43157,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>增加头痛专诊量，提升偏头痛诊断率，提高患者归拢率，增加门诊标签</t>
-        </is>
-      </c>
       <c r="Y273" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -43410,11 +43279,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
       <c r="Y274" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -43537,11 +43401,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
       <c r="Y275" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -43664,11 +43523,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
       <c r="Y276" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -43791,11 +43645,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
       <c r="Y277" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -43918,11 +43767,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X278" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
       <c r="Y278" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -44045,11 +43889,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>融动加入头痛专诊，提升偏头痛诊断率，提高患者归拢率</t>
-        </is>
-      </c>
       <c r="Y279" t="inlineStr">
         <is>
           <t>1、邀请参加GD会议，学习交流其他区域优质病例，方案，学习足量足疗程治疗，尽早治疗2、做好患者管理，每周两次诊后拜访，收集正反馈病例，增强用药信心</t>
@@ -44408,7 +44247,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
@@ -44537,7 +44376,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>96</t>
         </is>
       </c>
       <c r="U283" t="inlineStr">
@@ -44553,11 +44392,6 @@
       <c r="W283" t="inlineStr">
         <is>
           <t>130</t>
-        </is>
-      </c>
-      <c r="X283" t="inlineStr">
-        <is>
-          <t>提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
         </is>
       </c>
       <c r="Y283" t="inlineStr">
@@ -44665,7 +44499,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>128</t>
         </is>
       </c>
       <c r="U284" t="inlineStr">
@@ -44681,11 +44515,6 @@
       <c r="W284" t="inlineStr">
         <is>
           <t>130</t>
-        </is>
-      </c>
-      <c r="X284" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
         </is>
       </c>
       <c r="Y284" t="inlineStr">
@@ -44811,11 +44640,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="X285" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
       <c r="Y285" t="inlineStr">
         <is>
           <t>1、沟通加入眩晕门诊，归拢患者
@@ -44939,11 +44763,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X286" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
       <c r="Y286" t="inlineStr">
         <is>
           <t>1、与耳鼻喉科开展学术会议交流，突破vm患者2、拓展患者类型（低中高CM/MOH,月偏），借助学术会议，实现新拓展画像破冰
@@ -45067,11 +44886,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="X287" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
       <c r="Y287" t="inlineStr">
         <is>
           <t>1、与耳鼻喉科开展学术会议交流，突破vm患者2、拓展患者类型（低中高CM/MOH,月偏），借助学术会议，实现新拓展画像破冰
@@ -45195,11 +45009,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="X288" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
       <c r="Y288" t="inlineStr">
         <is>
           <t>1、沟通加入眩晕门诊，归拢患者
@@ -45323,11 +45132,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="X289" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
       <c r="Y289" t="inlineStr">
         <is>
           <t>1、沟通加入眩晕门诊，归拢患者
@@ -45451,11 +45255,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X290" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
       <c r="Y290" t="inlineStr">
         <is>
           <t>1、与耳鼻喉科开展学术会议交流，突破vm患者2、拓展患者类型（低中高CM/MOH,月偏），借助学术会议，实现新拓展画像破冰
@@ -45580,11 +45379,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X291" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
       <c r="Y291" t="inlineStr">
         <is>
           <t>1、沟通增加眩晕门诊，归拢患者
@@ -45708,17 +45502,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X292" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
-      <c r="Y292" t="inlineStr">
-        <is>
-          <t>1、沟通增加眩晕门诊，归拢患者
-2、明确VM患者画像，每周二病房拜访一次做好患者管理病例收集3、每次诊前提前沟通好足量足疗程方案，加强足疗程理念</t>
-        </is>
-      </c>
       <c r="Z292" t="inlineStr">
         <is>
           <t>三方会1场/季度</t>
@@ -45836,18 +45619,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X293" t="inlineStr">
-        <is>
-          <t>增加专诊量，提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
-      <c r="Y293" t="inlineStr">
-        <is>
-          <t>1、与耳鼻喉科开展学术会议交流，突破vm患者2、拓展患者类型（低中高CM/MOH,月偏），借助学术会议，实现新拓展画像破冰
-3、门诊前提醒诊后门诊当天复盘患者，加强足疗程理念
-4、增加专诊量，沟通增加挂号数至15个</t>
-        </is>
-      </c>
       <c r="Z293" t="inlineStr">
         <is>
           <t>三方会1场/季度</t>
@@ -45965,17 +45736,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X294" t="inlineStr">
-        <is>
-          <t>提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
-      <c r="Y294" t="inlineStr">
-        <is>
-          <t>1、与耳鼻喉科开展学术会议交流，突破vm患者2、拓展患者类型（低中高CM/MOH,月偏），借助学术会议，实现新拓展画像破冰
-3、门诊前提醒诊后门诊当天复盘患者，加强足疗程理念</t>
-        </is>
-      </c>
       <c r="Z294" t="inlineStr">
         <is>
           <t>三方会1场/季度</t>
@@ -46093,17 +45853,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="X295" t="inlineStr">
-        <is>
-          <t>提升偏头痛诊断率，提高患者归拢率，拓展患者画像</t>
-        </is>
-      </c>
-      <c r="Y295" t="inlineStr">
-        <is>
-          <t>1、与耳鼻喉科开展学术会议交流，突破vm患者2、拓展患者类型（低中高CM/MOH,月偏），借助学术会议，实现新拓展画像破冰
-4、门诊前提醒诊后门诊当天复盘患者，加强足疗程理念</t>
-        </is>
-      </c>
       <c r="Z295" t="inlineStr">
         <is>
           <t>三方会1场/季度</t>
@@ -47098,7 +46847,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>100</t>
         </is>
       </c>
       <c r="U303" t="inlineStr">
@@ -48876,7 +48625,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U317" t="inlineStr">
@@ -50400,7 +50149,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U329" t="inlineStr">
@@ -53550,7 +53299,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>216</t>
         </is>
       </c>
       <c r="U354" t="inlineStr">
@@ -55206,7 +54955,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U367" t="inlineStr">
@@ -55460,7 +55209,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="U369" t="inlineStr">
@@ -56095,7 +55844,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>40</t>
         </is>
       </c>
       <c r="U374" t="inlineStr">
@@ -56222,7 +55971,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U375" t="inlineStr">
@@ -56603,7 +56352,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U378" t="inlineStr">
@@ -59157,7 +58906,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>352</t>
         </is>
       </c>
       <c r="U398" t="inlineStr">
@@ -59177,9 +58926,9 @@
       </c>
       <c r="X398" t="inlineStr">
         <is>
-          <t>院外引流延长DOT减少限量影响
-提高VM诊断率
-PSR每月定期复盘，共识目标，解决需求</t>
+          <t>1,院外引流延长DOT减少限量影响
+2,提高VM诊断率
+3,PSR每月定期复盘，共识目标，解决需求</t>
         </is>
       </c>
       <c r="Y398" t="inlineStr">
@@ -59309,9 +59058,9 @@
       </c>
       <c r="X399" t="inlineStr">
         <is>
-          <t>VM诊断率
-中低频患者推荐话术
-DOT延长</t>
+          <t>1.VM诊断率
+2.中低频患者推荐话术
+3.DOT延长</t>
         </is>
       </c>
       <c r="Y399" t="inlineStr">
@@ -59442,12 +59191,15 @@
       </c>
       <c r="X400" t="inlineStr">
         <is>
-          <t>提高推荐率和复诊率</t>
+          <t>1.利用科室影响力拓展其他C类客户
+2.PSR随访归拢老患者，提高门诊VM患者比例
+3.正反馈患者100%返回门诊复配+给予信心</t>
         </is>
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>正反馈跟进外部先进诊断理念分享</t>
+          <t>1.利用其用药经验影响李Y,邬XF
+2.提高已使用患者复诊率，提高用药信心</t>
         </is>
       </c>
       <c r="Z400" t="inlineStr">
@@ -59569,14 +59321,16 @@
       </c>
       <c r="X401" t="inlineStr">
         <is>
-          <t>偏头痛诊断率
-VM诊断率、推荐率</t>
+          <t>1.OP复诊率提高
+2.GD、LB覆盖科室圈子
+3、NHC项目融动</t>
         </is>
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>PSR协助完成CDSS提高诊断率
-VM外部大会参会学习诊断</t>
+          <t>1.每月固定1场GD、LB覆盖圈子
+2.协助完成CDSSPSR随访老患者两周后正反馈100复诊循环
+、3NHC项目融动规划.共识每月目标拆分到周，定期提醒</t>
         </is>
       </c>
       <c r="Z401" t="inlineStr">
@@ -59699,17 +59453,22 @@
       </c>
       <c r="X402" t="inlineStr">
         <is>
-          <t>共病焦虑抑郁偏头痛诊断率</t>
+          <t>1、共病焦虑抑郁偏头痛诊断率
+2、短视频账号宣传引流
+3、赵Z影响观念</t>
         </is>
       </c>
       <c r="Y402" t="inlineStr">
         <is>
-          <t>多询问病史联合用药同时解决偏头痛和睡眠、情绪问题</t>
+          <t>1、每周固定拜访至少1-2次跟进共病正反馈病例制作科内分
+2、赵Z圈子影响观念，打造焦虑抑郁圈子
+3、协助剪辑完善短视频账号引流头痛头晕患者</t>
         </is>
       </c>
       <c r="Z402" t="inlineStr">
         <is>
-          <t>PO、三方覆盖</t>
+          <t>PO、三方覆盖
+赵Z相关会议讲课</t>
         </is>
       </c>
     </row>
@@ -59826,17 +59585,21 @@
       </c>
       <c r="X403" t="inlineStr">
         <is>
-          <t>高频词拜访获得科室支持</t>
+          <t>1.高频拜访、参与科室头痛头晕亚专业发展规划获得科室支持
+2.提高瑞美使用率影响科室其他B类客户</t>
         </is>
       </c>
       <c r="Y403" t="inlineStr">
         <is>
-          <t>定期拜访、活动覆盖得到科主任支持，增设科室内头痛眩晕小组医生</t>
+          <t>1、每周固定拜访至少1-2次
+2、VM使用正反馈跟进，病例制作科内分享
+3、每月两次汇报协助科室发展已做和准备做，了解科室内部需求精准解决</t>
         </is>
       </c>
       <c r="Z403" t="inlineStr">
         <is>
-          <t>PO、三方覆盖</t>
+          <t>院间交流会
+国家级资源/项目倾斜</t>
         </is>
       </c>
     </row>
@@ -59953,17 +59716,17 @@
       </c>
       <c r="X404" t="inlineStr">
         <is>
-          <t>治疗必要性</t>
+          <t>1、提高偏头痛诊断率</t>
         </is>
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>收集正反馈，提升信心</t>
+          <t>每周固定拜访至少1-2次，头痛主诉患者多问病史提高诊断率</t>
         </is>
       </c>
       <c r="Z404" t="inlineStr">
         <is>
-          <t>GD、LB覆盖</t>
+          <t>GD覆盖</t>
         </is>
       </c>
     </row>
@@ -60080,12 +59843,12 @@
       </c>
       <c r="X405" t="inlineStr">
         <is>
-          <t>提高推荐率和复诊率</t>
+          <t>提高推荐率</t>
         </is>
       </c>
       <c r="Y405" t="inlineStr">
         <is>
-          <t>psr做好患者管理</t>
+          <t>高频词拜访提高推荐率</t>
         </is>
       </c>
       <c r="Z405" t="inlineStr">
@@ -60332,6 +60095,26 @@
           <t>30</t>
         </is>
       </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>1、既往诊断VM但没采用CGRP治疗患者流失
+2、神经内科刚开展前庭检查，归拢科室内头晕主诉患者
+3、认可曹ZS，利用曹用药正反馈影响观念</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>1、分享神经内科使用经验，联合用药治疗
+2、个人发展规划和目标设定，打造中青年耳鼻喉圈子
+3、曹ZS正反馈整理分享</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>三方覆盖
+外部大型会议参会学习/讨论</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -60827,17 +60610,18 @@
       </c>
       <c r="X411" t="inlineStr">
         <is>
-          <t>3M推荐率</t>
+          <t>科内影响力大，决定亚专业发展</t>
         </is>
       </c>
       <c r="Y411" t="inlineStr">
         <is>
-          <t>加强足量足疗程话术沟通</t>
+          <t>1、每月定期汇报亚专业发展进展得到支持</t>
         </is>
       </c>
       <c r="Z411" t="inlineStr">
         <is>
-          <t>GD、LB覆盖</t>
+          <t>院间交流会
+国家级资源/项目倾斜</t>
         </is>
       </c>
     </row>
@@ -60954,7 +60738,7 @@
       </c>
       <c r="X412" t="inlineStr">
         <is>
-          <t>VM推荐率</t>
+          <t>提高VM推荐率</t>
         </is>
       </c>
       <c r="Y412" t="inlineStr">
@@ -61335,7 +61119,7 @@
       </c>
       <c r="X415" t="inlineStr">
         <is>
-          <t>推荐率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y415" t="inlineStr">
@@ -61462,7 +61246,7 @@
       </c>
       <c r="X416" t="inlineStr">
         <is>
-          <t>诊断率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y416" t="inlineStr">
@@ -61589,7 +61373,7 @@
       </c>
       <c r="X417" t="inlineStr">
         <is>
-          <t>推荐率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y417" t="inlineStr">
@@ -61716,7 +61500,7 @@
       </c>
       <c r="X418" t="inlineStr">
         <is>
-          <t>诊断率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y418" t="inlineStr">
@@ -61843,7 +61627,7 @@
       </c>
       <c r="X419" t="inlineStr">
         <is>
-          <t>复诊率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y419" t="inlineStr">
@@ -61970,7 +61754,7 @@
       </c>
       <c r="X420" t="inlineStr">
         <is>
-          <t>诊断率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y420" t="inlineStr">
@@ -62097,7 +61881,7 @@
       </c>
       <c r="X421" t="inlineStr">
         <is>
-          <t>诊断率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y421" t="inlineStr">
@@ -62585,7 +62369,7 @@
       </c>
       <c r="X425" t="inlineStr">
         <is>
-          <t>患者归拢率</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y425" t="inlineStr">
@@ -62707,7 +62491,7 @@
       </c>
       <c r="X426" t="inlineStr">
         <is>
-          <t>推荐率；DOT</t>
+          <t>提高诊断率和推荐率</t>
         </is>
       </c>
       <c r="Y426" t="inlineStr">
@@ -62921,7 +62705,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>616</t>
         </is>
       </c>
       <c r="U428" t="inlineStr">
@@ -63052,7 +62836,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>316</t>
         </is>
       </c>
       <c r="U429" t="inlineStr">
@@ -63583,7 +63367,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U433" t="inlineStr">
@@ -65690,7 +65474,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U449" t="inlineStr">
@@ -66730,7 +66514,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U457" t="inlineStr">
@@ -66796,7 +66580,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -66881,7 +66665,7 @@
       </c>
       <c r="X458" t="inlineStr">
         <is>
-          <t>维持治痛管理观念层级并扩大患者覆盖。挂号系统显示其无专病门诊设置、月均16个半天非专诊（无专诊模块），8月tth 148片且近5月稳步上行。机会点：依托抑郁焦虑亚专业推动开设『头痛-情绪共病』专病门诊/增加号源，扩大偏头痛-共病患者触达，并通过全病程治痛管理路径延长单患者管理时长。</t>
+          <t>通过全病程治痛管理路径延长单患者管理时长。</t>
         </is>
       </c>
       <c r="Y458" t="inlineStr">
@@ -67381,7 +67165,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U462" t="inlineStr">
@@ -67511,7 +67295,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U463" t="inlineStr">
@@ -67770,7 +67554,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U465" t="inlineStr">
@@ -69938,7 +69722,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>204</t>
         </is>
       </c>
       <c r="U482" t="inlineStr">
@@ -69958,20 +69742,24 @@
       </c>
       <c r="X482" t="inlineStr">
         <is>
-          <t>PPPD共病VM诊断率
-VM患者DOT延长</t>
+          <t>1.提高PPPD共病VM诊断率
+2.明确VM患者DOT延长达到短期治痛/晕
+3.住院部眩晕患者尝试推荐、其它主诉OP配药增加复诊间隔，增加门诊新患者
+4、专病门诊增加</t>
         </is>
       </c>
       <c r="Y482" t="inlineStr">
         <is>
-          <t>通过协助入组研究延长DOT
-刘凯鸣、张甦琳影响PPPD和VM时间界限，提高共病诊断率</t>
+          <t>1、刘凯鸣、张甦琳影响PPPD和VM诊断时间界限，提高共病诊断率
+2、通过得到科主任支持，提高专家门诊-专病门诊转变速度成立头痛头晕小组
+3、公众号文章宣传，短视频拍摄引流新患者。
+4、OP延长配药时间，非头痛头晕患者引流到专家门诊，提高专病门诊归拢率</t>
         </is>
       </c>
       <c r="Z482" t="inlineStr">
         <is>
-          <t>江苏省眩晕学会任职
-医学部协助完成VM研究
+          <t>江苏省眩晕学会管理任职
+医学部协助拜访完成需求
 全国眩晕平台授课提高知名度</t>
         </is>
       </c>
@@ -70089,14 +69877,15 @@
       </c>
       <c r="X483" t="inlineStr">
         <is>
-          <t>偏头痛患者提高推荐率、延长DOT
-VM提高诊断率</t>
+          <t>1、VM患者尝试诊断使用，归拢主诉头晕患者
+2、偏头痛患者推荐率</t>
         </is>
       </c>
       <c r="Y483" t="inlineStr">
         <is>
-          <t>典型偏头痛做到100%推荐
-VM相关学术活动参会学习诊断</t>
+          <t>1、每周1-2次拜访典型偏头痛做到100%推荐
+2、VM相关学术活动参会学习诊断
+3、每月一场LB覆盖打造自己圈子拓展B类客户</t>
         </is>
       </c>
       <c r="Z483" t="inlineStr">
@@ -70346,17 +70135,20 @@
       </c>
       <c r="X485" t="inlineStr">
         <is>
-          <t>高频词拜访获得科室支持</t>
+          <t>1.获得科室支持发展头痛头晕中西医治疗特色亚专业
+2.影响观念，科主任带头首选CGRP治疗方案</t>
         </is>
       </c>
       <c r="Y485" t="inlineStr">
         <is>
-          <t>定期拜访、活动覆盖得到科主任支持，增设科室内头痛眩晕小组医生</t>
+          <t>1.定期拜访一周至少1-2次、活动覆盖得到科内支持
+2.增设科室内头痛眩晕小组医生，打造中西特色科室</t>
         </is>
       </c>
       <c r="Z485" t="inlineStr">
         <is>
-          <t>PO、三方覆盖</t>
+          <t>三方覆盖
+老板共访规划科室头痛头晕发展</t>
         </is>
       </c>
     </row>
@@ -70986,7 +70778,7 @@
       </c>
       <c r="Z490" t="inlineStr">
         <is>
-          <t>GD、LB覆盖</t>
+          <t>GD覆盖</t>
         </is>
       </c>
     </row>
@@ -72303,7 +72095,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>120</t>
         </is>
       </c>
       <c r="U501" t="inlineStr">
@@ -72430,7 +72222,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="U502" t="inlineStr">
@@ -75830,7 +75622,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="U529" t="inlineStr">
@@ -77735,7 +77527,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U544" t="inlineStr">
@@ -78116,7 +77908,7 @@
       </c>
       <c r="S547" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="U547" t="inlineStr">
@@ -79024,6 +78816,65 @@
         </is>
       </c>
     </row>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
